--- a/deliverables/vimeo_upgrade_case.xlsx
+++ b/deliverables/vimeo_upgrade_case.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test design" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test readout" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value of test" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -154,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +197,10 @@
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,12 +209,9 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -594,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C27"/>
+  <dimension ref="B2:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -741,93 +743,105 @@
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Value of test</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Each category's revenue change split into volume and price.</t>
+          <t>Launch now, do nothing, or test first: each option's value under two priors.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Segments</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Subscribers, ARPU, bookings and revenue from the filings.</t>
+          <t>Each category's revenue change split into volume and price.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>Segments</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Revenue, costs and margins from the XBRL facts.</t>
+          <t>Subscribers, ARPU, bookings and revenue from the filings.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>P&amp;L</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Every assumption, with its reason.</t>
+          <t>Revenue, costs and margins from the XBRL facts.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Every assumption, with its reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>Reconciliation</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Each figure checked against the Python pipeline.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C23" s="9">
+      <c r="C24" s="9">
         <f>Reconciliation!B3</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Vimeo, Inc. 10-K and 10-Q filings with the SEC, 2021 to Q3 2025. Assumptions are mine and labelled. The test readout is simulated. Nothing here uses non-public information.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Domenico Perroni</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>https://github.com/D0M3N1C0X/vimeo-growth-case</t>
         </is>
@@ -840,12 +854,13 @@
     <hyperlink ref="B14" location="'Sensitivity'!A1"/>
     <hyperlink ref="B15" location="'Test design'!A1"/>
     <hyperlink ref="B16" location="'Test readout'!A1"/>
-    <hyperlink ref="B17" location="'Bridge'!A1"/>
-    <hyperlink ref="B18" location="'Segments'!A1"/>
-    <hyperlink ref="B19" location="'P&amp;L'!A1"/>
-    <hyperlink ref="B20" location="'Inputs'!A1"/>
-    <hyperlink ref="B21" location="'Reconciliation'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId1"/>
+    <hyperlink ref="B17" location="'Value of test'!A1"/>
+    <hyperlink ref="B18" location="'Bridge'!A1"/>
+    <hyperlink ref="B19" location="'Segments'!A1"/>
+    <hyperlink ref="B20" location="'P&amp;L'!A1"/>
+    <hyperlink ref="B21" location="'Inputs'!A1"/>
+    <hyperlink ref="B22" location="'Reconciliation'!A1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -853,6 +868,624 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>P&amp;L from XBRL facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>US$ millions. Blue figures from data/sec_financials.csv; ratios are formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="22" t="inlineStr"/>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="n">
+        <v>391.678</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>433.028</v>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>417.214</v>
+      </c>
+      <c r="E5" s="43" t="n">
+        <v>417.006</v>
+      </c>
+      <c r="F5" s="43" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="G5" s="43" t="n">
+        <v>104.376</v>
+      </c>
+      <c r="H5" s="43" t="n">
+        <v>104.564</v>
+      </c>
+      <c r="I5" s="43" t="n">
+        <v>103.034</v>
+      </c>
+      <c r="J5" s="43" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="K5" s="43" t="n">
+        <v>105.756</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>102.537</v>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>103.595</v>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>91.57599999999999</v>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>90.73099999999999</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <v>23.443</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>22.678</v>
+      </c>
+      <c r="H6" s="43" t="n">
+        <v>21.708</v>
+      </c>
+      <c r="I6" s="43" t="n">
+        <v>24.054</v>
+      </c>
+      <c r="J6" s="43" t="n">
+        <v>23.147</v>
+      </c>
+      <c r="K6" s="43" t="n">
+        <v>23.414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Sales and marketing</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>152.691</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>170.401</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>151.487</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>119.869</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <v>32.305</v>
+      </c>
+      <c r="G7" s="43" t="n">
+        <v>27.676</v>
+      </c>
+      <c r="H7" s="43" t="n">
+        <v>28.799</v>
+      </c>
+      <c r="I7" s="43" t="n">
+        <v>33.358</v>
+      </c>
+      <c r="J7" s="43" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="K7" s="43" t="n">
+        <v>30.44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n">
+        <v>105.586</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>127.661</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>107.074</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>109.373</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>28.135</v>
+      </c>
+      <c r="G8" s="43" t="n">
+        <v>26.972</v>
+      </c>
+      <c r="H8" s="43" t="n">
+        <v>26.588</v>
+      </c>
+      <c r="I8" s="43" t="n">
+        <v>31.186</v>
+      </c>
+      <c r="J8" s="43" t="n">
+        <v>29.789</v>
+      </c>
+      <c r="K8" s="43" t="n">
+        <v>31.208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>85.111</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>107.011</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>49.194</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>76.604</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>18.034</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>19.087</v>
+      </c>
+      <c r="H9" s="43" t="n">
+        <v>19.655</v>
+      </c>
+      <c r="I9" s="43" t="n">
+        <v>20.137</v>
+      </c>
+      <c r="J9" s="43" t="n">
+        <v>17.194</v>
+      </c>
+      <c r="K9" s="43" t="n">
+        <v>24.832</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="n">
+        <v>-61.016</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>-82.938</v>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>13.047</v>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>18.683</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>2.589</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>7.461</v>
+      </c>
+      <c r="H10" s="43" t="n">
+        <v>7.365</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>-6.092</v>
+      </c>
+      <c r="J10" s="43" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="K10" s="43" t="n">
+        <v>-4.591</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B13" s="45">
+        <f>1-B6/B5</f>
+        <v/>
+      </c>
+      <c r="C13" s="45">
+        <f>1-C6/C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="45">
+        <f>1-D6/D5</f>
+        <v/>
+      </c>
+      <c r="E13" s="45">
+        <f>1-E6/E5</f>
+        <v/>
+      </c>
+      <c r="F13" s="45">
+        <f>1-F6/F5</f>
+        <v/>
+      </c>
+      <c r="G13" s="45">
+        <f>1-G6/G5</f>
+        <v/>
+      </c>
+      <c r="H13" s="45">
+        <f>1-H6/H5</f>
+        <v/>
+      </c>
+      <c r="I13" s="45">
+        <f>1-I6/I5</f>
+        <v/>
+      </c>
+      <c r="J13" s="45">
+        <f>1-J6/J5</f>
+        <v/>
+      </c>
+      <c r="K13" s="45">
+        <f>1-K6/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Sales and marketing, % revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="45">
+        <f>B7/B5</f>
+        <v/>
+      </c>
+      <c r="C14" s="45">
+        <f>C7/C5</f>
+        <v/>
+      </c>
+      <c r="D14" s="45">
+        <f>D7/D5</f>
+        <v/>
+      </c>
+      <c r="E14" s="45">
+        <f>E7/E5</f>
+        <v/>
+      </c>
+      <c r="F14" s="45">
+        <f>F7/F5</f>
+        <v/>
+      </c>
+      <c r="G14" s="45">
+        <f>G7/G5</f>
+        <v/>
+      </c>
+      <c r="H14" s="45">
+        <f>H7/H5</f>
+        <v/>
+      </c>
+      <c r="I14" s="45">
+        <f>I7/I5</f>
+        <v/>
+      </c>
+      <c r="J14" s="45">
+        <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K14" s="45">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Research and development, % revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="45">
+        <f>B8/B5</f>
+        <v/>
+      </c>
+      <c r="C15" s="45">
+        <f>C8/C5</f>
+        <v/>
+      </c>
+      <c r="D15" s="45">
+        <f>D8/D5</f>
+        <v/>
+      </c>
+      <c r="E15" s="45">
+        <f>E8/E5</f>
+        <v/>
+      </c>
+      <c r="F15" s="45">
+        <f>F8/F5</f>
+        <v/>
+      </c>
+      <c r="G15" s="45">
+        <f>G8/G5</f>
+        <v/>
+      </c>
+      <c r="H15" s="45">
+        <f>H8/H5</f>
+        <v/>
+      </c>
+      <c r="I15" s="45">
+        <f>I8/I5</f>
+        <v/>
+      </c>
+      <c r="J15" s="45">
+        <f>J8/J5</f>
+        <v/>
+      </c>
+      <c r="K15" s="45">
+        <f>K8/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>General and administrative, % revenue</t>
+        </is>
+      </c>
+      <c r="B16" s="45">
+        <f>B9/B5</f>
+        <v/>
+      </c>
+      <c r="C16" s="45">
+        <f>C9/C5</f>
+        <v/>
+      </c>
+      <c r="D16" s="45">
+        <f>D9/D5</f>
+        <v/>
+      </c>
+      <c r="E16" s="45">
+        <f>E9/E5</f>
+        <v/>
+      </c>
+      <c r="F16" s="45">
+        <f>F9/F5</f>
+        <v/>
+      </c>
+      <c r="G16" s="45">
+        <f>G9/G5</f>
+        <v/>
+      </c>
+      <c r="H16" s="45">
+        <f>H9/H5</f>
+        <v/>
+      </c>
+      <c r="I16" s="45">
+        <f>I9/I5</f>
+        <v/>
+      </c>
+      <c r="J16" s="45">
+        <f>J9/J5</f>
+        <v/>
+      </c>
+      <c r="K16" s="45">
+        <f>K9/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Operating margin</t>
+        </is>
+      </c>
+      <c r="B17" s="45">
+        <f>B10/B5</f>
+        <v/>
+      </c>
+      <c r="C17" s="45">
+        <f>C10/C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="45">
+        <f>D10/D5</f>
+        <v/>
+      </c>
+      <c r="E17" s="45">
+        <f>E10/E5</f>
+        <v/>
+      </c>
+      <c r="F17" s="45">
+        <f>F10/F5</f>
+        <v/>
+      </c>
+      <c r="G17" s="45">
+        <f>G10/G5</f>
+        <v/>
+      </c>
+      <c r="H17" s="45">
+        <f>H10/H5</f>
+        <v/>
+      </c>
+      <c r="I17" s="45">
+        <f>I10/I5</f>
+        <v/>
+      </c>
+      <c r="J17" s="45">
+        <f>J10/J5</f>
+        <v/>
+      </c>
+      <c r="K17" s="45">
+        <f>K10/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Advertising, % revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="45">
+        <f>IF(B11="","",B11/B5)</f>
+        <v/>
+      </c>
+      <c r="C18" s="45">
+        <f>IF(C11="","",C11/C5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="45">
+        <f>IF(D11="","",D11/D5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="45">
+        <f>IF(E11="","",E11/E5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="45">
+        <f>IF(F11="","",F11/F5)</f>
+        <v/>
+      </c>
+      <c r="G18" s="45">
+        <f>IF(G11="","",G11/G5)</f>
+        <v/>
+      </c>
+      <c r="H18" s="45">
+        <f>IF(H11="","",H11/H5)</f>
+        <v/>
+      </c>
+      <c r="I18" s="45">
+        <f>IF(I11="","",I11/I5)</f>
+        <v/>
+      </c>
+      <c r="J18" s="45">
+        <f>IF(J11="","",J11/J5)</f>
+        <v/>
+      </c>
+      <c r="K18" s="45">
+        <f>IF(K11="","",K11/K5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -905,7 +1538,7 @@
           <t>Share of Self-Serve accounts with team-level signals</t>
         </is>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.02</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -920,7 +1553,7 @@
           <t>Extra upgrades per eligible account per year, caused by outreach</t>
         </is>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="47" t="n">
         <v>0.01</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -935,7 +1568,7 @@
           <t>First-year contract value, share of average Enterprise ARPU</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -950,7 +1583,7 @@
           <t>Net revenue retention of upgraded accounts after year one</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="D8" s="13" t="inlineStr"/>
@@ -961,7 +1594,7 @@
           <t>Upgrades stop paying their Self-Serve plan (1 = yes)</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n">
+      <c r="C9" s="49" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="inlineStr"/>
@@ -972,7 +1605,7 @@
           <t>Fully loaded cost of one account executive per year</t>
         </is>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="50" t="n">
         <v>180000</v>
       </c>
       <c r="D10" s="13" t="inlineStr"/>
@@ -994,7 +1627,7 @@
           <t>Uplift the team is hired for</t>
         </is>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="37" t="n">
         <v>0.01</v>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1009,7 +1642,7 @@
           <t>Outreach cost per eligible account per year</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="51" t="n">
         <v>30</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -1024,7 +1657,7 @@
           <t>Gross margin on the new revenue</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C14" s="38" t="n">
         <v>0.78</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -1039,7 +1672,7 @@
           <t>One-off build of scoring and routing</t>
         </is>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="50" t="n">
         <v>400000</v>
       </c>
       <c r="D15" s="13" t="inlineStr"/>
@@ -1050,7 +1683,7 @@
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C16" s="38" t="n">
         <v>0.1</v>
       </c>
       <c r="D16" s="13" t="inlineStr"/>
@@ -1061,7 +1694,7 @@
           <t>Test: significance level</t>
         </is>
       </c>
-      <c r="C17" s="45" t="n">
+      <c r="C17" s="38" t="n">
         <v>0.05</v>
       </c>
       <c r="D17" s="13" t="inlineStr"/>
@@ -1072,7 +1705,7 @@
           <t>Test: power</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n">
+      <c r="C18" s="38" t="n">
         <v>0.8</v>
       </c>
       <c r="D18" s="13" t="inlineStr"/>
@@ -1083,7 +1716,7 @@
           <t>Test: organic upgrades per eligible account in 90 days</t>
         </is>
       </c>
-      <c r="C19" s="43" t="n">
+      <c r="C19" s="47" t="n">
         <v>0.004</v>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -1098,7 +1731,7 @@
           <t>Test: Self-Serve cancellations in 90 days</t>
         </is>
       </c>
-      <c r="C20" s="50" t="n">
+      <c r="C20" s="39" t="n">
         <v>0.03</v>
       </c>
       <c r="D20" s="13" t="inlineStr"/>
@@ -1109,7 +1742,7 @@
           <t>Test: largest rise in cancellations accepted, per 90 days</t>
         </is>
       </c>
-      <c r="C21" s="48" t="n">
+      <c r="C21" s="37" t="n">
         <v>0.005</v>
       </c>
       <c r="D21" s="13" t="inlineStr"/>
@@ -1120,13 +1753,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1787,7 @@
     </row>
     <row r="3">
       <c r="B3" s="36">
-        <f>IF(COUNTIF(G7:G192,"No")=0,"All "&amp;COUNTA(B7:B192)&amp;" checks match",COUNTIF(G7:G192,"No")&amp;" of "&amp;COUNTA(B7:B192)&amp;" checks do not match")</f>
+        <f>IF(COUNTIF(G7:G215,"No")=0,"All "&amp;COUNTA(B7:B215)&amp;" checks match",COUNTIF(G7:G215,"No")&amp;" of "&amp;COUNTA(B7:B215)&amp;" checks do not match")</f>
         <v/>
       </c>
     </row>
@@ -1202,14 +1835,14 @@
           <t>2021 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="52" t="n">
         <v>23619.6</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="53">
         <f>Segments!J6</f>
         <v/>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="54">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(E7)),E7-D7,"")</f>
         <v/>
       </c>
@@ -1229,14 +1862,14 @@
           <t>2022 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D8" s="51" t="n">
+      <c r="D8" s="52" t="n">
         <v>38609.9</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="53">
         <f>Segments!J9</f>
         <v/>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="54">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8)),E8-D8,"")</f>
         <v/>
       </c>
@@ -1256,14 +1889,14 @@
           <t>2023 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D9" s="51" t="n">
+      <c r="D9" s="52" t="n">
         <v>56753.2</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="53">
         <f>Segments!J12</f>
         <v/>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="54">
         <f>IF(AND(ISNUMBER(D9),ISNUMBER(E9)),E9-D9,"")</f>
         <v/>
       </c>
@@ -1283,14 +1916,14 @@
           <t>2024 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D10" s="51" t="n">
+      <c r="D10" s="52" t="n">
         <v>84193.5</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="53">
         <f>Segments!J15</f>
         <v/>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="54">
         <f>IF(AND(ISNUMBER(D10),ISNUMBER(E10)),E10-D10,"")</f>
         <v/>
       </c>
@@ -1310,14 +1943,14 @@
           <t>2024Q1 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D11" s="51" t="n">
+      <c r="D11" s="52" t="n">
         <v>18451.24453551913</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="53">
         <f>Segments!J18</f>
         <v/>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="54">
         <f>IF(AND(ISNUMBER(D11),ISNUMBER(E11)),E11-D11,"")</f>
         <v/>
       </c>
@@ -1337,14 +1970,14 @@
           <t>2024Q2 OTT ARPU x average</t>
         </is>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="52" t="n">
         <v>12760.1393442623</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="53">
         <f>Segments!J24</f>
         <v/>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="54">
         <f>IF(AND(ISNUMBER(D12),ISNUMBER(E12)),E12-D12,"")</f>
         <v/>
       </c>
@@ -1364,14 +1997,14 @@
           <t>2024Q3 Self-Serve ARPU x average</t>
         </is>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="52" t="n">
         <v>58400.29289617486</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="53">
         <f>Segments!J27</f>
         <v/>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="54">
         <f>IF(AND(ISNUMBER(D13),ISNUMBER(E13)),E13-D13,"")</f>
         <v/>
       </c>
@@ -1391,14 +2024,14 @@
           <t>2025Q1 Vimeo Enterprise ARPU x average</t>
         </is>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="52" t="n">
         <v>24286.68493150685</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="53">
         <f>Segments!J33</f>
         <v/>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="54">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),E14-D14,"")</f>
         <v/>
       </c>
@@ -1418,14 +2051,14 @@
           <t>2025Q2 OTT ARPU x average</t>
         </is>
       </c>
-      <c r="D15" s="51" t="n">
+      <c r="D15" s="52" t="n">
         <v>12149.62191780822</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="53">
         <f>Segments!J39</f>
         <v/>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="54">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),E15-D15,"")</f>
         <v/>
       </c>
@@ -1445,14 +2078,14 @@
           <t>2025Q3 Self-Serve ARPU x average</t>
         </is>
       </c>
-      <c r="D16" s="51" t="n">
+      <c r="D16" s="52" t="n">
         <v>58730.98520547945</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="53">
         <f>Segments!J42</f>
         <v/>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="54">
         <f>IF(AND(ISNUMBER(D16),ISNUMBER(E16)),E16-D16,"")</f>
         <v/>
       </c>
@@ -1472,14 +2105,14 @@
           <t>Largest ARPU x average gap</t>
         </is>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="52" t="n">
         <v>0.01683430521249774</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="53">
         <f>Segments!K48</f>
         <v/>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="54">
         <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17)),E17-D17,"")</f>
         <v/>
       </c>
@@ -1499,14 +2132,14 @@
           <t>2021 Gross margin</t>
         </is>
       </c>
-      <c r="D18" s="51" t="n">
+      <c r="D18" s="52" t="n">
         <v>0.7382109794269782</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <f>'P&amp;L'!B13</f>
         <v/>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="54">
         <f>IF(AND(ISNUMBER(D18),ISNUMBER(E18)),E18-D18,"")</f>
         <v/>
       </c>
@@ -1526,14 +2159,14 @@
           <t>2022 Gross margin</t>
         </is>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="52" t="n">
         <v>0.7607660474611342</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>'P&amp;L'!C13</f>
         <v/>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="54">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(E19)),E19-D19,"")</f>
         <v/>
       </c>
@@ -1553,14 +2186,14 @@
           <t>2023 Gross margin</t>
         </is>
       </c>
-      <c r="D20" s="51" t="n">
+      <c r="D20" s="52" t="n">
         <v>0.7805059274137494</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="53">
         <f>'P&amp;L'!D13</f>
         <v/>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="54">
         <f>IF(AND(ISNUMBER(D20),ISNUMBER(E20)),E20-D20,"")</f>
         <v/>
       </c>
@@ -1580,14 +2213,14 @@
           <t>2024 Gross margin</t>
         </is>
       </c>
-      <c r="D21" s="51" t="n">
+      <c r="D21" s="52" t="n">
         <v>0.7824227948758531</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="53">
         <f>'P&amp;L'!E13</f>
         <v/>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="54">
         <f>IF(AND(ISNUMBER(D21),ISNUMBER(E21)),E21-D21,"")</f>
         <v/>
       </c>
@@ -1607,14 +2240,14 @@
           <t>2024Q1 Gross margin</t>
         </is>
       </c>
-      <c r="D22" s="51" t="n">
+      <c r="D22" s="52" t="n">
         <v>0.7765417977313888</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="53">
         <f>'P&amp;L'!F13</f>
         <v/>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="54">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22)),E22-D22,"")</f>
         <v/>
       </c>
@@ -1634,14 +2267,14 @@
           <t>2024Q2 Gross margin</t>
         </is>
       </c>
-      <c r="D23" s="51" t="n">
+      <c r="D23" s="52" t="n">
         <v>0.7827278301525255</v>
       </c>
-      <c r="E23" s="52">
+      <c r="E23" s="53">
         <f>'P&amp;L'!G13</f>
         <v/>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="54">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(E23)),E23-D23,"")</f>
         <v/>
       </c>
@@ -1661,14 +2294,14 @@
           <t>2024Q3 Gross margin</t>
         </is>
       </c>
-      <c r="D24" s="51" t="n">
+      <c r="D24" s="52" t="n">
         <v>0.7923950881756627</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="53">
         <f>'P&amp;L'!H13</f>
         <v/>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="54">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24)),E24-D24,"")</f>
         <v/>
       </c>
@@ -1688,14 +2321,14 @@
           <t>2025Q1 Gross margin</t>
         </is>
       </c>
-      <c r="D25" s="51" t="n">
+      <c r="D25" s="52" t="n">
         <v>0.7665430828658502</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="53">
         <f>'P&amp;L'!I13</f>
         <v/>
       </c>
-      <c r="F25" s="53">
+      <c r="F25" s="54">
         <f>IF(AND(ISNUMBER(D25),ISNUMBER(E25)),E25-D25,"")</f>
         <v/>
       </c>
@@ -1715,14 +2348,14 @@
           <t>2025Q2 Gross margin</t>
         </is>
       </c>
-      <c r="D26" s="51" t="n">
+      <c r="D26" s="52" t="n">
         <v>0.7788150979455327</v>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="53">
         <f>'P&amp;L'!J13</f>
         <v/>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="54">
         <f>IF(AND(ISNUMBER(D26),ISNUMBER(E26)),E26-D26,"")</f>
         <v/>
       </c>
@@ -1742,14 +2375,14 @@
           <t>2025Q3 Gross margin</t>
         </is>
       </c>
-      <c r="D27" s="51" t="n">
+      <c r="D27" s="52" t="n">
         <v>0.7786035780475812</v>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="53">
         <f>'P&amp;L'!K13</f>
         <v/>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="54">
         <f>IF(AND(ISNUMBER(D27),ISNUMBER(E27)),E27-D27,"")</f>
         <v/>
       </c>
@@ -1769,14 +2402,14 @@
           <t>2021 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D28" s="51" t="n">
+      <c r="D28" s="52" t="n">
         <v>0.3898380812810523</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="53">
         <f>'P&amp;L'!B14</f>
         <v/>
       </c>
-      <c r="F28" s="53">
+      <c r="F28" s="54">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28)),E28-D28,"")</f>
         <v/>
       </c>
@@ -1796,14 +2429,14 @@
           <t>2022 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D29" s="51" t="n">
+      <c r="D29" s="52" t="n">
         <v>0.393510350369953</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="53">
         <f>'P&amp;L'!C14</f>
         <v/>
       </c>
-      <c r="F29" s="53">
+      <c r="F29" s="54">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),E29-D29,"")</f>
         <v/>
       </c>
@@ -1823,14 +2456,14 @@
           <t>2023 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D30" s="51" t="n">
+      <c r="D30" s="52" t="n">
         <v>0.3630918425556189</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="53">
         <f>'P&amp;L'!D14</f>
         <v/>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="54">
         <f>IF(AND(ISNUMBER(D30),ISNUMBER(E30)),E30-D30,"")</f>
         <v/>
       </c>
@@ -1850,14 +2483,14 @@
           <t>2024 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D31" s="51" t="n">
+      <c r="D31" s="52" t="n">
         <v>0.2874514994988082</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="53">
         <f>'P&amp;L'!E14</f>
         <v/>
       </c>
-      <c r="F31" s="53">
+      <c r="F31" s="54">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31)),E31-D31,"")</f>
         <v/>
       </c>
@@ -1877,14 +2510,14 @@
           <t>2024Q1 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D32" s="51" t="n">
+      <c r="D32" s="52" t="n">
         <v>0.3079306071871128</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="53">
         <f>'P&amp;L'!F14</f>
         <v/>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="54">
         <f>IF(AND(ISNUMBER(D32),ISNUMBER(E32)),E32-D32,"")</f>
         <v/>
       </c>
@@ -1904,14 +2537,14 @@
           <t>2024Q2 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D33" s="51" t="n">
+      <c r="D33" s="52" t="n">
         <v>0.2651567410132597</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="53">
         <f>'P&amp;L'!G14</f>
         <v/>
       </c>
-      <c r="F33" s="53">
+      <c r="F33" s="54">
         <f>IF(AND(ISNUMBER(D33),ISNUMBER(E33)),E33-D33,"")</f>
         <v/>
       </c>
@@ -1931,14 +2564,14 @@
           <t>2024Q3 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D34" s="51" t="n">
+      <c r="D34" s="52" t="n">
         <v>0.2754198385677671</v>
       </c>
-      <c r="E34" s="52">
+      <c r="E34" s="53">
         <f>'P&amp;L'!H14</f>
         <v/>
       </c>
-      <c r="F34" s="53">
+      <c r="F34" s="54">
         <f>IF(AND(ISNUMBER(D34),ISNUMBER(E34)),E34-D34,"")</f>
         <v/>
       </c>
@@ -1958,14 +2591,14 @@
           <t>2025Q1 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D35" s="51" t="n">
+      <c r="D35" s="52" t="n">
         <v>0.3237572063590659</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="53">
         <f>'P&amp;L'!I14</f>
         <v/>
       </c>
-      <c r="F35" s="53">
+      <c r="F35" s="54">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35)),E35-D35,"")</f>
         <v/>
       </c>
@@ -1985,14 +2618,14 @@
           <t>2025Q2 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D36" s="51" t="n">
+      <c r="D36" s="52" t="n">
         <v>0.2891543239369326</v>
       </c>
-      <c r="E36" s="52">
+      <c r="E36" s="53">
         <f>'P&amp;L'!J14</f>
         <v/>
       </c>
-      <c r="F36" s="53">
+      <c r="F36" s="54">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36)),E36-D36,"")</f>
         <v/>
       </c>
@@ -2012,14 +2645,14 @@
           <t>2025Q3 Sales and marketing, % revenue</t>
         </is>
       </c>
-      <c r="D37" s="51" t="n">
+      <c r="D37" s="52" t="n">
         <v>0.2878323688490488</v>
       </c>
-      <c r="E37" s="52">
+      <c r="E37" s="53">
         <f>'P&amp;L'!K14</f>
         <v/>
       </c>
-      <c r="F37" s="53">
+      <c r="F37" s="54">
         <f>IF(AND(ISNUMBER(D37),ISNUMBER(E37)),E37-D37,"")</f>
         <v/>
       </c>
@@ -2039,14 +2672,14 @@
           <t>2021 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D38" s="51" t="n">
+      <c r="D38" s="52" t="n">
         <v>0.2695734761717533</v>
       </c>
-      <c r="E38" s="52">
+      <c r="E38" s="53">
         <f>'P&amp;L'!B15</f>
         <v/>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="54">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(E38)),E38-D38,"")</f>
         <v/>
       </c>
@@ -2066,14 +2699,14 @@
           <t>2022 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D39" s="51" t="n">
+      <c r="D39" s="52" t="n">
         <v>0.2948100353787746</v>
       </c>
-      <c r="E39" s="52">
+      <c r="E39" s="53">
         <f>'P&amp;L'!C15</f>
         <v/>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="54">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(E39)),E39-D39,"")</f>
         <v/>
       </c>
@@ -2093,14 +2726,14 @@
           <t>2023 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D40" s="51" t="n">
+      <c r="D40" s="52" t="n">
         <v>0.2566404770693217</v>
       </c>
-      <c r="E40" s="52">
+      <c r="E40" s="53">
         <f>'P&amp;L'!D15</f>
         <v/>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="54">
         <f>IF(AND(ISNUMBER(D40),ISNUMBER(E40)),E40-D40,"")</f>
         <v/>
       </c>
@@ -2120,14 +2753,14 @@
           <t>2024 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D41" s="51" t="n">
+      <c r="D41" s="52" t="n">
         <v>0.2622815978666974</v>
       </c>
-      <c r="E41" s="52">
+      <c r="E41" s="53">
         <f>'P&amp;L'!E15</f>
         <v/>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="54">
         <f>IF(AND(ISNUMBER(D41),ISNUMBER(E41)),E41-D41,"")</f>
         <v/>
       </c>
@@ -2147,14 +2780,14 @@
           <t>2024Q1 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D42" s="51" t="n">
+      <c r="D42" s="52" t="n">
         <v>0.268182251453627</v>
       </c>
-      <c r="E42" s="52">
+      <c r="E42" s="53">
         <f>'P&amp;L'!F15</f>
         <v/>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="54">
         <f>IF(AND(ISNUMBER(D42),ISNUMBER(E42)),E42-D42,"")</f>
         <v/>
       </c>
@@ -2174,14 +2807,14 @@
           <t>2024Q2 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D43" s="51" t="n">
+      <c r="D43" s="52" t="n">
         <v>0.2584118954548938</v>
       </c>
-      <c r="E43" s="52">
+      <c r="E43" s="53">
         <f>'P&amp;L'!G15</f>
         <v/>
       </c>
-      <c r="F43" s="53">
+      <c r="F43" s="54">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),E43-D43,"")</f>
         <v/>
       </c>
@@ -2201,14 +2834,14 @@
           <t>2024Q3 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D44" s="51" t="n">
+      <c r="D44" s="52" t="n">
         <v>0.254274893844918</v>
       </c>
-      <c r="E44" s="52">
+      <c r="E44" s="53">
         <f>'P&amp;L'!H15</f>
         <v/>
       </c>
-      <c r="F44" s="53">
+      <c r="F44" s="54">
         <f>IF(AND(ISNUMBER(D44),ISNUMBER(E44)),E44-D44,"")</f>
         <v/>
       </c>
@@ -2228,14 +2861,14 @@
           <t>2025Q1 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D45" s="51" t="n">
+      <c r="D45" s="52" t="n">
         <v>0.3026767863035503</v>
       </c>
-      <c r="E45" s="52">
+      <c r="E45" s="53">
         <f>'P&amp;L'!I15</f>
         <v/>
       </c>
-      <c r="F45" s="53">
+      <c r="F45" s="54">
         <f>IF(AND(ISNUMBER(D45),ISNUMBER(E45)),E45-D45,"")</f>
         <v/>
       </c>
@@ -2255,14 +2888,14 @@
           <t>2025Q2 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D46" s="51" t="n">
+      <c r="D46" s="52" t="n">
         <v>0.2846536072623029</v>
       </c>
-      <c r="E46" s="52">
+      <c r="E46" s="53">
         <f>'P&amp;L'!J15</f>
         <v/>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="54">
         <f>IF(AND(ISNUMBER(D46),ISNUMBER(E46)),E46-D46,"")</f>
         <v/>
       </c>
@@ -2282,14 +2915,14 @@
           <t>2025Q3 Research and development, % revenue</t>
         </is>
       </c>
-      <c r="D47" s="51" t="n">
+      <c r="D47" s="52" t="n">
         <v>0.2950943681682363</v>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="53">
         <f>'P&amp;L'!K15</f>
         <v/>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="54">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(E47)),E47-D47,"")</f>
         <v/>
       </c>
@@ -2309,14 +2942,14 @@
           <t>2021 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D48" s="51" t="n">
+      <c r="D48" s="52" t="n">
         <v>0.2172983930677751</v>
       </c>
-      <c r="E48" s="52">
+      <c r="E48" s="53">
         <f>'P&amp;L'!B16</f>
         <v/>
       </c>
-      <c r="F48" s="53">
+      <c r="F48" s="54">
         <f>IF(AND(ISNUMBER(D48),ISNUMBER(E48)),E48-D48,"")</f>
         <v/>
       </c>
@@ -2336,14 +2969,14 @@
           <t>2022 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D49" s="51" t="n">
+      <c r="D49" s="52" t="n">
         <v>0.2471225879157929</v>
       </c>
-      <c r="E49" s="52">
+      <c r="E49" s="53">
         <f>'P&amp;L'!C16</f>
         <v/>
       </c>
-      <c r="F49" s="53">
+      <c r="F49" s="54">
         <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49)),E49-D49,"")</f>
         <v/>
       </c>
@@ -2363,14 +2996,14 @@
           <t>2023 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D50" s="51" t="n">
+      <c r="D50" s="52" t="n">
         <v>0.1179107124880757</v>
       </c>
-      <c r="E50" s="52">
+      <c r="E50" s="53">
         <f>'P&amp;L'!D16</f>
         <v/>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="54">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50)),E50-D50,"")</f>
         <v/>
       </c>
@@ -2390,14 +3023,14 @@
           <t>2024 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D51" s="51" t="n">
+      <c r="D51" s="52" t="n">
         <v>0.1836999947242965</v>
       </c>
-      <c r="E51" s="52">
+      <c r="E51" s="53">
         <f>'P&amp;L'!E16</f>
         <v/>
       </c>
-      <c r="F51" s="53">
+      <c r="F51" s="54">
         <f>IF(AND(ISNUMBER(D51),ISNUMBER(E51)),E51-D51,"")</f>
         <v/>
       </c>
@@ -2417,14 +3050,14 @@
           <t>2024Q1 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D52" s="51" t="n">
+      <c r="D52" s="52" t="n">
         <v>0.171899723572586</v>
       </c>
-      <c r="E52" s="52">
+      <c r="E52" s="53">
         <f>'P&amp;L'!F16</f>
         <v/>
       </c>
-      <c r="F52" s="53">
+      <c r="F52" s="54">
         <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52)),E52-D52,"")</f>
         <v/>
       </c>
@@ -2444,14 +3077,14 @@
           <t>2024Q2 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D53" s="51" t="n">
+      <c r="D53" s="52" t="n">
         <v>0.1828677090518893</v>
       </c>
-      <c r="E53" s="52">
+      <c r="E53" s="53">
         <f>'P&amp;L'!G16</f>
         <v/>
       </c>
-      <c r="F53" s="53">
+      <c r="F53" s="54">
         <f>IF(AND(ISNUMBER(D53),ISNUMBER(E53)),E53-D53,"")</f>
         <v/>
       </c>
@@ -2471,14 +3104,14 @@
           <t>2024Q3 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D54" s="51" t="n">
+      <c r="D54" s="52" t="n">
         <v>0.1879710034046135</v>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="53">
         <f>'P&amp;L'!H16</f>
         <v/>
       </c>
-      <c r="F54" s="53">
+      <c r="F54" s="54">
         <f>IF(AND(ISNUMBER(D54),ISNUMBER(E54)),E54-D54,"")</f>
         <v/>
       </c>
@@ -2498,14 +3131,14 @@
           <t>2025Q1 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D55" s="51" t="n">
+      <c r="D55" s="52" t="n">
         <v>0.1954403400819147</v>
       </c>
-      <c r="E55" s="52">
+      <c r="E55" s="53">
         <f>'P&amp;L'!I16</f>
         <v/>
       </c>
-      <c r="F55" s="53">
+      <c r="F55" s="54">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(E55)),E55-D55,"")</f>
         <v/>
       </c>
@@ -2525,14 +3158,14 @@
           <t>2025Q2 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D56" s="51" t="n">
+      <c r="D56" s="52" t="n">
         <v>0.1643000477783086</v>
       </c>
-      <c r="E56" s="52">
+      <c r="E56" s="53">
         <f>'P&amp;L'!J16</f>
         <v/>
       </c>
-      <c r="F56" s="53">
+      <c r="F56" s="54">
         <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56)),E56-D56,"")</f>
         <v/>
       </c>
@@ -2552,14 +3185,14 @@
           <t>2025Q3 General and administrative, % revenue</t>
         </is>
       </c>
-      <c r="D57" s="51" t="n">
+      <c r="D57" s="52" t="n">
         <v>0.2348046446537312</v>
       </c>
-      <c r="E57" s="52">
+      <c r="E57" s="53">
         <f>'P&amp;L'!K16</f>
         <v/>
       </c>
-      <c r="F57" s="53">
+      <c r="F57" s="54">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57)),E57-D57,"")</f>
         <v/>
       </c>
@@ -2579,14 +3212,14 @@
           <t>2021 Operating margin</t>
         </is>
       </c>
-      <c r="D58" s="51" t="n">
+      <c r="D58" s="52" t="n">
         <v>-0.1557810242086612</v>
       </c>
-      <c r="E58" s="52">
+      <c r="E58" s="53">
         <f>'P&amp;L'!B17</f>
         <v/>
       </c>
-      <c r="F58" s="53">
+      <c r="F58" s="54">
         <f>IF(AND(ISNUMBER(D58),ISNUMBER(E58)),E58-D58,"")</f>
         <v/>
       </c>
@@ -2606,14 +3239,14 @@
           <t>2022 Operating margin</t>
         </is>
       </c>
-      <c r="D59" s="51" t="n">
+      <c r="D59" s="52" t="n">
         <v>-0.1915303398394561</v>
       </c>
-      <c r="E59" s="52">
+      <c r="E59" s="53">
         <f>'P&amp;L'!C17</f>
         <v/>
       </c>
-      <c r="F59" s="53">
+      <c r="F59" s="54">
         <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59)),E59-D59,"")</f>
         <v/>
       </c>
@@ -2633,14 +3266,14 @@
           <t>2023 Operating margin</t>
         </is>
       </c>
-      <c r="D60" s="51" t="n">
+      <c r="D60" s="52" t="n">
         <v>0.03127172146668137</v>
       </c>
-      <c r="E60" s="52">
+      <c r="E60" s="53">
         <f>'P&amp;L'!D17</f>
         <v/>
       </c>
-      <c r="F60" s="53">
+      <c r="F60" s="54">
         <f>IF(AND(ISNUMBER(D60),ISNUMBER(E60)),E60-D60,"")</f>
         <v/>
       </c>
@@ -2660,14 +3293,14 @@
           <t>2024 Operating margin</t>
         </is>
       </c>
-      <c r="D61" s="51" t="n">
+      <c r="D61" s="52" t="n">
         <v>0.0448027126708009</v>
       </c>
-      <c r="E61" s="52">
+      <c r="E61" s="53">
         <f>'P&amp;L'!E17</f>
         <v/>
       </c>
-      <c r="F61" s="53">
+      <c r="F61" s="54">
         <f>IF(AND(ISNUMBER(D61),ISNUMBER(E61)),E61-D61,"")</f>
         <v/>
       </c>
@@ -2687,14 +3320,14 @@
           <t>2024Q1 Operating margin</t>
         </is>
       </c>
-      <c r="D62" s="51" t="n">
+      <c r="D62" s="52" t="n">
         <v>0.02467829568201315</v>
       </c>
-      <c r="E62" s="52">
+      <c r="E62" s="53">
         <f>'P&amp;L'!F17</f>
         <v/>
       </c>
-      <c r="F62" s="53">
+      <c r="F62" s="54">
         <f>IF(AND(ISNUMBER(D62),ISNUMBER(E62)),E62-D62,"")</f>
         <v/>
       </c>
@@ -2714,14 +3347,14 @@
           <t>2024Q2 Operating margin</t>
         </is>
       </c>
-      <c r="D63" s="51" t="n">
+      <c r="D63" s="52" t="n">
         <v>0.07148194987353415</v>
       </c>
-      <c r="E63" s="52">
+      <c r="E63" s="53">
         <f>'P&amp;L'!G17</f>
         <v/>
       </c>
-      <c r="F63" s="53">
+      <c r="F63" s="54">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63)),E63-D63,"")</f>
         <v/>
       </c>
@@ -2741,14 +3374,14 @@
           <t>2024Q3 Operating margin</t>
         </is>
       </c>
-      <c r="D64" s="51" t="n">
+      <c r="D64" s="52" t="n">
         <v>0.07043533147163461</v>
       </c>
-      <c r="E64" s="52">
+      <c r="E64" s="53">
         <f>'P&amp;L'!H17</f>
         <v/>
       </c>
-      <c r="F64" s="53">
+      <c r="F64" s="54">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64)),E64-D64,"")</f>
         <v/>
       </c>
@@ -2768,14 +3401,14 @@
           <t>2025Q1 Operating margin</t>
         </is>
       </c>
-      <c r="D65" s="51" t="n">
+      <c r="D65" s="52" t="n">
         <v>-0.05912611371003745</v>
       </c>
-      <c r="E65" s="52">
+      <c r="E65" s="53">
         <f>'P&amp;L'!I17</f>
         <v/>
       </c>
-      <c r="F65" s="53">
+      <c r="F65" s="54">
         <f>IF(AND(ISNUMBER(D65),ISNUMBER(E65)),E65-D65,"")</f>
         <v/>
       </c>
@@ -2795,14 +3428,14 @@
           <t>2025Q2 Operating margin</t>
         </is>
       </c>
-      <c r="D66" s="51" t="n">
+      <c r="D66" s="52" t="n">
         <v>0.03558528428093646</v>
       </c>
-      <c r="E66" s="52">
+      <c r="E66" s="53">
         <f>'P&amp;L'!J17</f>
         <v/>
       </c>
-      <c r="F66" s="53">
+      <c r="F66" s="54">
         <f>IF(AND(ISNUMBER(D66),ISNUMBER(E66)),E66-D66,"")</f>
         <v/>
       </c>
@@ -2822,14 +3455,14 @@
           <t>2025Q3 Operating margin</t>
         </is>
       </c>
-      <c r="D67" s="51" t="n">
+      <c r="D67" s="52" t="n">
         <v>-0.04341124853436212</v>
       </c>
-      <c r="E67" s="52">
+      <c r="E67" s="53">
         <f>'P&amp;L'!K17</f>
         <v/>
       </c>
-      <c r="F67" s="53">
+      <c r="F67" s="54">
         <f>IF(AND(ISNUMBER(D67),ISNUMBER(E67)),E67-D67,"")</f>
         <v/>
       </c>
@@ -2849,14 +3482,14 @@
           <t>2021 Advertising, % revenue</t>
         </is>
       </c>
-      <c r="D68" s="51" t="n">
+      <c r="D68" s="52" t="n">
         <v>0.2223765439978758</v>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="53">
         <f>'P&amp;L'!B18</f>
         <v/>
       </c>
-      <c r="F68" s="53">
+      <c r="F68" s="54">
         <f>IF(AND(ISNUMBER(D68),ISNUMBER(E68)),E68-D68,"")</f>
         <v/>
       </c>
@@ -2876,14 +3509,14 @@
           <t>2022 Advertising, % revenue</t>
         </is>
       </c>
-      <c r="D69" s="51" t="n">
+      <c r="D69" s="52" t="n">
         <v>0.1764320090155833</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="53">
         <f>'P&amp;L'!C18</f>
         <v/>
       </c>
-      <c r="F69" s="53">
+      <c r="F69" s="54">
         <f>IF(AND(ISNUMBER(D69),ISNUMBER(E69)),E69-D69,"")</f>
         <v/>
       </c>
@@ -2903,14 +3536,14 @@
           <t>2023 Advertising, % revenue</t>
         </is>
       </c>
-      <c r="D70" s="51" t="n">
+      <c r="D70" s="52" t="n">
         <v>0.1447698303508511</v>
       </c>
-      <c r="E70" s="52">
+      <c r="E70" s="53">
         <f>'P&amp;L'!D18</f>
         <v/>
       </c>
-      <c r="F70" s="53">
+      <c r="F70" s="54">
         <f>IF(AND(ISNUMBER(D70),ISNUMBER(E70)),E70-D70,"")</f>
         <v/>
       </c>
@@ -2930,14 +3563,14 @@
           <t>2024 Advertising, % revenue</t>
         </is>
       </c>
-      <c r="D71" s="51" t="n">
+      <c r="D71" s="52" t="n">
         <v>0.07769672378814693</v>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="53">
         <f>'P&amp;L'!E18</f>
         <v/>
       </c>
-      <c r="F71" s="53">
+      <c r="F71" s="54">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71)),E71-D71,"")</f>
         <v/>
       </c>
@@ -2957,14 +3590,14 @@
           <t>2021-2022 Self-Serve &amp; Add-Ons volume</t>
         </is>
       </c>
-      <c r="D72" s="51" t="n">
+      <c r="D72" s="52" t="n">
         <v>16.82850000000004</v>
       </c>
-      <c r="E72" s="52">
+      <c r="E72" s="53">
         <f>Bridge!F5</f>
         <v/>
       </c>
-      <c r="F72" s="53">
+      <c r="F72" s="54">
         <f>IF(AND(ISNUMBER(D72),ISNUMBER(E72)),E72-D72,"")</f>
         <v/>
       </c>
@@ -2984,14 +3617,14 @@
           <t>2021-2022 Self-Serve &amp; Add-Ons price</t>
         </is>
       </c>
-      <c r="D73" s="51" t="n">
+      <c r="D73" s="52" t="n">
         <v>11.894</v>
       </c>
-      <c r="E73" s="52">
+      <c r="E73" s="53">
         <f>Bridge!G5</f>
         <v/>
       </c>
-      <c r="F73" s="53">
+      <c r="F73" s="54">
         <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73)),E73-D73,"")</f>
         <v/>
       </c>
@@ -3011,14 +3644,14 @@
           <t>2021-2022 Self-Serve &amp; Add-Ons change</t>
         </is>
       </c>
-      <c r="D74" s="51" t="n">
+      <c r="D74" s="52" t="n">
         <v>29.46699999999998</v>
       </c>
-      <c r="E74" s="52">
+      <c r="E74" s="53">
         <f>Bridge!I5</f>
         <v/>
       </c>
-      <c r="F74" s="53">
+      <c r="F74" s="54">
         <f>IF(AND(ISNUMBER(D74),ISNUMBER(E74)),E74-D74,"")</f>
         <v/>
       </c>
@@ -3038,14 +3671,14 @@
           <t>2021-2022 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D75" s="51" t="n">
+      <c r="D75" s="52" t="n">
         <v>14.0014</v>
       </c>
-      <c r="E75" s="52">
+      <c r="E75" s="53">
         <f>Bridge!F6</f>
         <v/>
       </c>
-      <c r="F75" s="53">
+      <c r="F75" s="54">
         <f>IF(AND(ISNUMBER(D75),ISNUMBER(E75)),E75-D75,"")</f>
         <v/>
       </c>
@@ -3065,14 +3698,14 @@
           <t>2021-2022 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D76" s="51" t="n">
+      <c r="D76" s="52" t="n">
         <v>0.9888999999999999</v>
       </c>
-      <c r="E76" s="52">
+      <c r="E76" s="53">
         <f>Bridge!G6</f>
         <v/>
       </c>
-      <c r="F76" s="53">
+      <c r="F76" s="54">
         <f>IF(AND(ISNUMBER(D76),ISNUMBER(E76)),E76-D76,"")</f>
         <v/>
       </c>
@@ -3092,14 +3725,14 @@
           <t>2021-2022 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D77" s="51" t="n">
+      <c r="D77" s="52" t="n">
         <v>16.035</v>
       </c>
-      <c r="E77" s="52">
+      <c r="E77" s="53">
         <f>Bridge!I6</f>
         <v/>
       </c>
-      <c r="F77" s="53">
+      <c r="F77" s="54">
         <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77)),E77-D77,"")</f>
         <v/>
       </c>
@@ -3119,14 +3752,14 @@
           <t>2021-2022 Other volume</t>
         </is>
       </c>
-      <c r="D78" s="51" t="n">
+      <c r="D78" s="52" t="n">
         <v>-34.372</v>
       </c>
-      <c r="E78" s="52">
+      <c r="E78" s="53">
         <f>Bridge!F7</f>
         <v/>
       </c>
-      <c r="F78" s="53">
+      <c r="F78" s="54">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78)),E78-D78,"")</f>
         <v/>
       </c>
@@ -3146,14 +3779,14 @@
           <t>2021-2022 Other price</t>
         </is>
       </c>
-      <c r="D79" s="51" t="n">
+      <c r="D79" s="52" t="n">
         <v>30.104</v>
       </c>
-      <c r="E79" s="52">
+      <c r="E79" s="53">
         <f>Bridge!G7</f>
         <v/>
       </c>
-      <c r="F79" s="53">
+      <c r="F79" s="54">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(E79)),E79-D79,"")</f>
         <v/>
       </c>
@@ -3173,14 +3806,14 @@
           <t>2021-2022 Other change</t>
         </is>
       </c>
-      <c r="D80" s="51" t="n">
+      <c r="D80" s="52" t="n">
         <v>-4.152000000000001</v>
       </c>
-      <c r="E80" s="52">
+      <c r="E80" s="53">
         <f>Bridge!I7</f>
         <v/>
       </c>
-      <c r="F80" s="53">
+      <c r="F80" s="54">
         <f>IF(AND(ISNUMBER(D80),ISNUMBER(E80)),E80-D80,"")</f>
         <v/>
       </c>
@@ -3200,14 +3833,14 @@
           <t>2022-2023 Self-Serve &amp; Add-Ons volume</t>
         </is>
       </c>
-      <c r="D81" s="51" t="n">
+      <c r="D81" s="52" t="n">
         <v>-17.36875</v>
       </c>
-      <c r="E81" s="52">
+      <c r="E81" s="53">
         <f>Bridge!F8</f>
         <v/>
       </c>
-      <c r="F81" s="53">
+      <c r="F81" s="54">
         <f>IF(AND(ISNUMBER(D81),ISNUMBER(E81)),E81-D81,"")</f>
         <v/>
       </c>
@@ -3227,14 +3860,14 @@
           <t>2022-2023 Self-Serve &amp; Add-Ons price</t>
         </is>
       </c>
-      <c r="D82" s="51" t="n">
+      <c r="D82" s="52" t="n">
         <v>-1.48615</v>
       </c>
-      <c r="E82" s="52">
+      <c r="E82" s="53">
         <f>Bridge!G8</f>
         <v/>
       </c>
-      <c r="F82" s="53">
+      <c r="F82" s="54">
         <f>IF(AND(ISNUMBER(D82),ISNUMBER(E82)),E82-D82,"")</f>
         <v/>
       </c>
@@ -3254,14 +3887,14 @@
           <t>2022-2023 Self-Serve &amp; Add-Ons change</t>
         </is>
       </c>
-      <c r="D83" s="51" t="n">
+      <c r="D83" s="52" t="n">
         <v>-19.197</v>
       </c>
-      <c r="E83" s="52">
+      <c r="E83" s="53">
         <f>Bridge!I8</f>
         <v/>
       </c>
-      <c r="F83" s="53">
+      <c r="F83" s="54">
         <f>IF(AND(ISNUMBER(D83),ISNUMBER(E83)),E83-D83,"")</f>
         <v/>
       </c>
@@ -3281,14 +3914,14 @@
           <t>2022-2023 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D84" s="51" t="n">
+      <c r="D84" s="52" t="n">
         <v>18.2655</v>
       </c>
-      <c r="E84" s="52">
+      <c r="E84" s="53">
         <f>Bridge!F9</f>
         <v/>
       </c>
-      <c r="F84" s="53">
+      <c r="F84" s="54">
         <f>IF(AND(ISNUMBER(D84),ISNUMBER(E84)),E84-D84,"")</f>
         <v/>
       </c>
@@ -3308,14 +3941,14 @@
           <t>2022-2023 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D85" s="51" t="n">
+      <c r="D85" s="52" t="n">
         <v>-0.1222</v>
       </c>
-      <c r="E85" s="52">
+      <c r="E85" s="53">
         <f>Bridge!G9</f>
         <v/>
       </c>
-      <c r="F85" s="53">
+      <c r="F85" s="54">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85)),E85-D85,"")</f>
         <v/>
       </c>
@@ -3335,14 +3968,14 @@
           <t>2022-2023 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D86" s="51" t="n">
+      <c r="D86" s="52" t="n">
         <v>17.228</v>
       </c>
-      <c r="E86" s="52">
+      <c r="E86" s="53">
         <f>Bridge!I9</f>
         <v/>
       </c>
-      <c r="F86" s="53">
+      <c r="F86" s="54">
         <f>IF(AND(ISNUMBER(D86),ISNUMBER(E86)),E86-D86,"")</f>
         <v/>
       </c>
@@ -3362,14 +3995,14 @@
           <t>2022-2023 Other volume</t>
         </is>
       </c>
-      <c r="D87" s="51" t="n">
+      <c r="D87" s="52" t="n">
         <v>-30.60475</v>
       </c>
-      <c r="E87" s="52">
+      <c r="E87" s="53">
         <f>Bridge!F10</f>
         <v/>
       </c>
-      <c r="F87" s="53">
+      <c r="F87" s="54">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(E87)),E87-D87,"")</f>
         <v/>
       </c>
@@ -3389,14 +4022,14 @@
           <t>2022-2023 Other price</t>
         </is>
       </c>
-      <c r="D88" s="51" t="n">
+      <c r="D88" s="52" t="n">
         <v>16.76655</v>
       </c>
-      <c r="E88" s="52">
+      <c r="E88" s="53">
         <f>Bridge!G10</f>
         <v/>
       </c>
-      <c r="F88" s="53">
+      <c r="F88" s="54">
         <f>IF(AND(ISNUMBER(D88),ISNUMBER(E88)),E88-D88,"")</f>
         <v/>
       </c>
@@ -3416,14 +4049,14 @@
           <t>2022-2023 Other change</t>
         </is>
       </c>
-      <c r="D89" s="51" t="n">
+      <c r="D89" s="52" t="n">
         <v>-13.845</v>
       </c>
-      <c r="E89" s="52">
+      <c r="E89" s="53">
         <f>Bridge!I10</f>
         <v/>
       </c>
-      <c r="F89" s="53">
+      <c r="F89" s="54">
         <f>IF(AND(ISNUMBER(D89),ISNUMBER(E89)),E89-D89,"")</f>
         <v/>
       </c>
@@ -3443,14 +4076,14 @@
           <t>2023-2024 Self-Serve &amp; Add-Ons volume</t>
         </is>
       </c>
-      <c r="D90" s="51" t="n">
+      <c r="D90" s="52" t="n">
         <v>-28.15610000000001</v>
       </c>
-      <c r="E90" s="52">
+      <c r="E90" s="53">
         <f>Bridge!F11</f>
         <v/>
       </c>
-      <c r="F90" s="53">
+      <c r="F90" s="54">
         <f>IF(AND(ISNUMBER(D90),ISNUMBER(E90)),E90-D90,"")</f>
         <v/>
       </c>
@@ -3470,14 +4103,14 @@
           <t>2023-2024 Self-Serve &amp; Add-Ons price</t>
         </is>
       </c>
-      <c r="D91" s="51" t="n">
+      <c r="D91" s="52" t="n">
         <v>13.7305</v>
       </c>
-      <c r="E91" s="52">
+      <c r="E91" s="53">
         <f>Bridge!G11</f>
         <v/>
       </c>
-      <c r="F91" s="53">
+      <c r="F91" s="54">
         <f>IF(AND(ISNUMBER(D91),ISNUMBER(E91)),E91-D91,"")</f>
         <v/>
       </c>
@@ -3497,14 +4130,14 @@
           <t>2023-2024 Self-Serve &amp; Add-Ons change</t>
         </is>
       </c>
-      <c r="D92" s="51" t="n">
+      <c r="D92" s="52" t="n">
         <v>-13.83800000000002</v>
       </c>
-      <c r="E92" s="52">
+      <c r="E92" s="53">
         <f>Bridge!I11</f>
         <v/>
       </c>
-      <c r="F92" s="53">
+      <c r="F92" s="54">
         <f>IF(AND(ISNUMBER(D92),ISNUMBER(E92)),E92-D92,"")</f>
         <v/>
       </c>
@@ -3524,14 +4157,14 @@
           <t>2023-2024 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D93" s="51" t="n">
+      <c r="D93" s="52" t="n">
         <v>19.36080000000001</v>
       </c>
-      <c r="E93" s="52">
+      <c r="E93" s="53">
         <f>Bridge!F12</f>
         <v/>
       </c>
-      <c r="F93" s="53">
+      <c r="F93" s="54">
         <f>IF(AND(ISNUMBER(D93),ISNUMBER(E93)),E93-D93,"")</f>
         <v/>
       </c>
@@ -3551,14 +4184,14 @@
           <t>2023-2024 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D94" s="51" t="n">
+      <c r="D94" s="52" t="n">
         <v>8.079499999999999</v>
       </c>
-      <c r="E94" s="52">
+      <c r="E94" s="53">
         <f>Bridge!G12</f>
         <v/>
       </c>
-      <c r="F94" s="53">
+      <c r="F94" s="54">
         <f>IF(AND(ISNUMBER(D94),ISNUMBER(E94)),E94-D94,"")</f>
         <v/>
       </c>
@@ -3578,14 +4211,14 @@
           <t>2023-2024 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D95" s="51" t="n">
+      <c r="D95" s="52" t="n">
         <v>26.692</v>
       </c>
-      <c r="E95" s="52">
+      <c r="E95" s="53">
         <f>Bridge!I12</f>
         <v/>
       </c>
-      <c r="F95" s="53">
+      <c r="F95" s="54">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(E95)),E95-D95,"")</f>
         <v/>
       </c>
@@ -3605,14 +4238,14 @@
           <t>2023-2024 Other volume</t>
         </is>
       </c>
-      <c r="D96" s="51" t="n">
+      <c r="D96" s="52" t="n">
         <v>-21.59999999999999</v>
       </c>
-      <c r="E96" s="52">
+      <c r="E96" s="53">
         <f>Bridge!F13</f>
         <v/>
       </c>
-      <c r="F96" s="53">
+      <c r="F96" s="54">
         <f>IF(AND(ISNUMBER(D96),ISNUMBER(E96)),E96-D96,"")</f>
         <v/>
       </c>
@@ -3632,14 +4265,14 @@
           <t>2023-2024 Other price</t>
         </is>
       </c>
-      <c r="D97" s="51" t="n">
+      <c r="D97" s="52" t="n">
         <v>8.5932</v>
       </c>
-      <c r="E97" s="52">
+      <c r="E97" s="53">
         <f>Bridge!G13</f>
         <v/>
       </c>
-      <c r="F97" s="53">
+      <c r="F97" s="54">
         <f>IF(AND(ISNUMBER(D97),ISNUMBER(E97)),E97-D97,"")</f>
         <v/>
       </c>
@@ -3659,14 +4292,14 @@
           <t>2023-2024 Other change</t>
         </is>
       </c>
-      <c r="D98" s="51" t="n">
+      <c r="D98" s="52" t="n">
         <v>-13.062</v>
       </c>
-      <c r="E98" s="52">
+      <c r="E98" s="53">
         <f>Bridge!I13</f>
         <v/>
       </c>
-      <c r="F98" s="53">
+      <c r="F98" s="54">
         <f>IF(AND(ISNUMBER(D98),ISNUMBER(E98)),E98-D98,"")</f>
         <v/>
       </c>
@@ -3686,14 +4319,14 @@
           <t>2024Q1-2025Q1 Self-Serve volume</t>
         </is>
       </c>
-      <c r="D99" s="51" t="n">
+      <c r="D99" s="52" t="n">
         <v>-6.835121769967803</v>
       </c>
-      <c r="E99" s="52">
+      <c r="E99" s="53">
         <f>Bridge!F14</f>
         <v/>
       </c>
-      <c r="F99" s="53">
+      <c r="F99" s="54">
         <f>IF(AND(ISNUMBER(D99),ISNUMBER(E99)),E99-D99,"")</f>
         <v/>
       </c>
@@ -3713,14 +4346,14 @@
           <t>2024Q1-2025Q1 Self-Serve price</t>
         </is>
       </c>
-      <c r="D100" s="51" t="n">
+      <c r="D100" s="52" t="n">
         <v>3.961382541732164</v>
       </c>
-      <c r="E100" s="52">
+      <c r="E100" s="53">
         <f>Bridge!G14</f>
         <v/>
       </c>
-      <c r="F100" s="53">
+      <c r="F100" s="54">
         <f>IF(AND(ISNUMBER(D100),ISNUMBER(E100)),E100-D100,"")</f>
         <v/>
       </c>
@@ -3740,14 +4373,14 @@
           <t>2024Q1-2025Q1 Self-Serve change</t>
         </is>
       </c>
-      <c r="D101" s="51" t="n">
+      <c r="D101" s="52" t="n">
         <v>-2.994999999999997</v>
       </c>
-      <c r="E101" s="52">
+      <c r="E101" s="53">
         <f>Bridge!I14</f>
         <v/>
       </c>
-      <c r="F101" s="53">
+      <c r="F101" s="54">
         <f>IF(AND(ISNUMBER(D101),ISNUMBER(E101)),E101-D101,"")</f>
         <v/>
       </c>
@@ -3767,14 +4400,14 @@
           <t>2024Q1-2025Q1 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D102" s="51" t="n">
+      <c r="D102" s="52" t="n">
         <v>2.835863846470545</v>
       </c>
-      <c r="E102" s="52">
+      <c r="E102" s="53">
         <f>Bridge!F15</f>
         <v/>
       </c>
-      <c r="F102" s="53">
+      <c r="F102" s="54">
         <f>IF(AND(ISNUMBER(D102),ISNUMBER(E102)),E102-D102,"")</f>
         <v/>
       </c>
@@ -3794,14 +4427,14 @@
           <t>2024Q1-2025Q1 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D103" s="51" t="n">
+      <c r="D103" s="52" t="n">
         <v>2.999576549517179</v>
       </c>
-      <c r="E103" s="52">
+      <c r="E103" s="53">
         <f>Bridge!G15</f>
         <v/>
       </c>
-      <c r="F103" s="53">
+      <c r="F103" s="54">
         <f>IF(AND(ISNUMBER(D103),ISNUMBER(E103)),E103-D103,"")</f>
         <v/>
       </c>
@@ -3821,14 +4454,14 @@
           <t>2024Q1-2025Q1 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D104" s="51" t="n">
+      <c r="D104" s="52" t="n">
         <v>5.957000000000001</v>
       </c>
-      <c r="E104" s="52">
+      <c r="E104" s="53">
         <f>Bridge!I15</f>
         <v/>
       </c>
-      <c r="F104" s="53">
+      <c r="F104" s="54">
         <f>IF(AND(ISNUMBER(D104),ISNUMBER(E104)),E104-D104,"")</f>
         <v/>
       </c>
@@ -3848,14 +4481,14 @@
           <t>2024Q1-2025Q1 OTT volume</t>
         </is>
       </c>
-      <c r="D105" s="51" t="n">
+      <c r="D105" s="52" t="n">
         <v>0.8179320345834276</v>
       </c>
-      <c r="E105" s="52">
+      <c r="E105" s="53">
         <f>Bridge!F16</f>
         <v/>
       </c>
-      <c r="F105" s="53">
+      <c r="F105" s="54">
         <f>IF(AND(ISNUMBER(D105),ISNUMBER(E105)),E105-D105,"")</f>
         <v/>
       </c>
@@ -3875,14 +4508,14 @@
           <t>2024Q1-2025Q1 OTT price</t>
         </is>
       </c>
-      <c r="D106" s="51" t="n">
+      <c r="D106" s="52" t="n">
         <v>-1.360364304962945</v>
       </c>
-      <c r="E106" s="52">
+      <c r="E106" s="53">
         <f>Bridge!G16</f>
         <v/>
       </c>
-      <c r="F106" s="53">
+      <c r="F106" s="54">
         <f>IF(AND(ISNUMBER(D106),ISNUMBER(E106)),E106-D106,"")</f>
         <v/>
       </c>
@@ -3902,14 +4535,14 @@
           <t>2024Q1-2025Q1 OTT change</t>
         </is>
       </c>
-      <c r="D107" s="51" t="n">
+      <c r="D107" s="52" t="n">
         <v>-0.8159999999999989</v>
       </c>
-      <c r="E107" s="52">
+      <c r="E107" s="53">
         <f>Bridge!I16</f>
         <v/>
       </c>
-      <c r="F107" s="53">
+      <c r="F107" s="54">
         <f>IF(AND(ISNUMBER(D107),ISNUMBER(E107)),E107-D107,"")</f>
         <v/>
       </c>
@@ -3929,14 +4562,14 @@
           <t>2024Q2-2025Q2 Self-Serve volume</t>
         </is>
       </c>
-      <c r="D108" s="51" t="n">
+      <c r="D108" s="52" t="n">
         <v>-6.858165988472185</v>
       </c>
-      <c r="E108" s="52">
+      <c r="E108" s="53">
         <f>Bridge!F17</f>
         <v/>
       </c>
-      <c r="F108" s="53">
+      <c r="F108" s="54">
         <f>IF(AND(ISNUMBER(D108),ISNUMBER(E108)),E108-D108,"")</f>
         <v/>
       </c>
@@ -3956,14 +4589,14 @@
           <t>2024Q2-2025Q2 Self-Serve price</t>
         </is>
       </c>
-      <c r="D109" s="51" t="n">
+      <c r="D109" s="52" t="n">
         <v>6.055064796766231</v>
       </c>
-      <c r="E109" s="52">
+      <c r="E109" s="53">
         <f>Bridge!G17</f>
         <v/>
       </c>
-      <c r="F109" s="53">
+      <c r="F109" s="54">
         <f>IF(AND(ISNUMBER(D109),ISNUMBER(E109)),E109-D109,"")</f>
         <v/>
       </c>
@@ -3983,14 +4616,14 @@
           <t>2024Q2-2025Q2 Self-Serve change</t>
         </is>
       </c>
-      <c r="D110" s="51" t="n">
+      <c r="D110" s="52" t="n">
         <v>-0.8190000000000026</v>
       </c>
-      <c r="E110" s="52">
+      <c r="E110" s="53">
         <f>Bridge!I17</f>
         <v/>
       </c>
-      <c r="F110" s="53">
+      <c r="F110" s="54">
         <f>IF(AND(ISNUMBER(D110),ISNUMBER(E110)),E110-D110,"")</f>
         <v/>
       </c>
@@ -4010,14 +4643,14 @@
           <t>2024Q2-2025Q2 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D111" s="51" t="n">
+      <c r="D111" s="52" t="n">
         <v>2.324711108615911</v>
       </c>
-      <c r="E111" s="52">
+      <c r="E111" s="53">
         <f>Bridge!F18</f>
         <v/>
       </c>
-      <c r="F111" s="53">
+      <c r="F111" s="54">
         <f>IF(AND(ISNUMBER(D111),ISNUMBER(E111)),E111-D111,"")</f>
         <v/>
       </c>
@@ -4037,14 +4670,14 @@
           <t>2024Q2-2025Q2 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D112" s="51" t="n">
+      <c r="D112" s="52" t="n">
         <v>2.710897765551314</v>
       </c>
-      <c r="E112" s="52">
+      <c r="E112" s="53">
         <f>Bridge!G18</f>
         <v/>
       </c>
-      <c r="F112" s="53">
+      <c r="F112" s="54">
         <f>IF(AND(ISNUMBER(D112),ISNUMBER(E112)),E112-D112,"")</f>
         <v/>
       </c>
@@ -4064,14 +4697,14 @@
           <t>2024Q2-2025Q2 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D113" s="51" t="n">
+      <c r="D113" s="52" t="n">
         <v>4.946000000000002</v>
       </c>
-      <c r="E113" s="52">
+      <c r="E113" s="53">
         <f>Bridge!I18</f>
         <v/>
       </c>
-      <c r="F113" s="53">
+      <c r="F113" s="54">
         <f>IF(AND(ISNUMBER(D113),ISNUMBER(E113)),E113-D113,"")</f>
         <v/>
       </c>
@@ -4091,14 +4724,14 @@
           <t>2024Q2-2025Q2 OTT volume</t>
         </is>
       </c>
-      <c r="D114" s="51" t="n">
+      <c r="D114" s="52" t="n">
         <v>0.408630632906655</v>
       </c>
-      <c r="E114" s="52">
+      <c r="E114" s="53">
         <f>Bridge!F19</f>
         <v/>
       </c>
-      <c r="F114" s="53">
+      <c r="F114" s="54">
         <f>IF(AND(ISNUMBER(D114),ISNUMBER(E114)),E114-D114,"")</f>
         <v/>
       </c>
@@ -4118,14 +4751,14 @@
           <t>2024Q2-2025Q2 OTT price</t>
         </is>
       </c>
-      <c r="D115" s="51" t="n">
+      <c r="D115" s="52" t="n">
         <v>-1.01914805936073</v>
       </c>
-      <c r="E115" s="52">
+      <c r="E115" s="53">
         <f>Bridge!G19</f>
         <v/>
       </c>
-      <c r="F115" s="53">
+      <c r="F115" s="54">
         <f>IF(AND(ISNUMBER(D115),ISNUMBER(E115)),E115-D115,"")</f>
         <v/>
       </c>
@@ -4145,14 +4778,14 @@
           <t>2024Q2-2025Q2 OTT change</t>
         </is>
       </c>
-      <c r="D116" s="51" t="n">
+      <c r="D116" s="52" t="n">
         <v>-0.3729999999999993</v>
       </c>
-      <c r="E116" s="52">
+      <c r="E116" s="53">
         <f>Bridge!I19</f>
         <v/>
       </c>
-      <c r="F116" s="53">
+      <c r="F116" s="54">
         <f>IF(AND(ISNUMBER(D116),ISNUMBER(E116)),E116-D116,"")</f>
         <v/>
       </c>
@@ -4172,14 +4805,14 @@
           <t>2024Q3-2025Q3 Self-Serve volume</t>
         </is>
       </c>
-      <c r="D117" s="51" t="n">
+      <c r="D117" s="52" t="n">
         <v>-6.851992721012044</v>
       </c>
-      <c r="E117" s="52">
+      <c r="E117" s="53">
         <f>Bridge!F20</f>
         <v/>
       </c>
-      <c r="F117" s="53">
+      <c r="F117" s="54">
         <f>IF(AND(ISNUMBER(D117),ISNUMBER(E117)),E117-D117,"")</f>
         <v/>
       </c>
@@ -4199,14 +4832,14 @@
           <t>2024Q3-2025Q3 Self-Serve price</t>
         </is>
       </c>
-      <c r="D118" s="51" t="n">
+      <c r="D118" s="52" t="n">
         <v>7.182685030316641</v>
       </c>
-      <c r="E118" s="52">
+      <c r="E118" s="53">
         <f>Bridge!G20</f>
         <v/>
       </c>
-      <c r="F118" s="53">
+      <c r="F118" s="54">
         <f>IF(AND(ISNUMBER(D118),ISNUMBER(E118)),E118-D118,"")</f>
         <v/>
       </c>
@@ -4226,14 +4859,14 @@
           <t>2024Q3-2025Q3 Self-Serve change</t>
         </is>
       </c>
-      <c r="D119" s="51" t="n">
+      <c r="D119" s="52" t="n">
         <v>0.3870000000000005</v>
       </c>
-      <c r="E119" s="52">
+      <c r="E119" s="53">
         <f>Bridge!I20</f>
         <v/>
       </c>
-      <c r="F119" s="53">
+      <c r="F119" s="54">
         <f>IF(AND(ISNUMBER(D119),ISNUMBER(E119)),E119-D119,"")</f>
         <v/>
       </c>
@@ -4253,14 +4886,14 @@
           <t>2024Q3-2025Q3 Vimeo Enterprise volume</t>
         </is>
       </c>
-      <c r="D120" s="51" t="n">
+      <c r="D120" s="52" t="n">
         <v>2.396891929036601</v>
       </c>
-      <c r="E120" s="52">
+      <c r="E120" s="53">
         <f>Bridge!F21</f>
         <v/>
       </c>
-      <c r="F120" s="53">
+      <c r="F120" s="54">
         <f>IF(AND(ISNUMBER(D120),ISNUMBER(E120)),E120-D120,"")</f>
         <v/>
       </c>
@@ -4280,14 +4913,14 @@
           <t>2024Q3-2025Q3 Vimeo Enterprise price</t>
         </is>
       </c>
-      <c r="D121" s="51" t="n">
+      <c r="D121" s="52" t="n">
         <v>1.560002452279363</v>
       </c>
-      <c r="E121" s="52">
+      <c r="E121" s="53">
         <f>Bridge!G21</f>
         <v/>
       </c>
-      <c r="F121" s="53">
+      <c r="F121" s="54">
         <f>IF(AND(ISNUMBER(D121),ISNUMBER(E121)),E121-D121,"")</f>
         <v/>
       </c>
@@ -4307,14 +4940,14 @@
           <t>2024Q3-2025Q3 Vimeo Enterprise change</t>
         </is>
       </c>
-      <c r="D122" s="51" t="n">
+      <c r="D122" s="52" t="n">
         <v>3.827999999999999</v>
       </c>
-      <c r="E122" s="52">
+      <c r="E122" s="53">
         <f>Bridge!I21</f>
         <v/>
       </c>
-      <c r="F122" s="53">
+      <c r="F122" s="54">
         <f>IF(AND(ISNUMBER(D122),ISNUMBER(E122)),E122-D122,"")</f>
         <v/>
       </c>
@@ -4334,14 +4967,14 @@
           <t>2024Q3-2025Q3 OTT volume</t>
         </is>
       </c>
-      <c r="D123" s="51" t="n">
+      <c r="D123" s="52" t="n">
         <v>0.3977209446814884</v>
       </c>
-      <c r="E123" s="52">
+      <c r="E123" s="53">
         <f>Bridge!F22</f>
         <v/>
       </c>
-      <c r="F123" s="53">
+      <c r="F123" s="54">
         <f>IF(AND(ISNUMBER(D123),ISNUMBER(E123)),E123-D123,"")</f>
         <v/>
       </c>
@@ -4361,14 +4994,14 @@
           <t>2024Q3-2025Q3 OTT price</t>
         </is>
       </c>
-      <c r="D124" s="51" t="n">
+      <c r="D124" s="52" t="n">
         <v>-0.8289557077625561</v>
       </c>
-      <c r="E124" s="52">
+      <c r="E124" s="53">
         <f>Bridge!G22</f>
         <v/>
       </c>
-      <c r="F124" s="53">
+      <c r="F124" s="54">
         <f>IF(AND(ISNUMBER(D124),ISNUMBER(E124)),E124-D124,"")</f>
         <v/>
       </c>
@@ -4388,14 +5021,14 @@
           <t>2024Q3-2025Q3 OTT change</t>
         </is>
       </c>
-      <c r="D125" s="51" t="n">
+      <c r="D125" s="52" t="n">
         <v>-0.4770000000000003</v>
       </c>
-      <c r="E125" s="52">
+      <c r="E125" s="53">
         <f>Bridge!I22</f>
         <v/>
       </c>
-      <c r="F125" s="53">
+      <c r="F125" s="54">
         <f>IF(AND(ISNUMBER(D125),ISNUMBER(E125)),E125-D125,"")</f>
         <v/>
       </c>
@@ -4415,14 +5048,14 @@
           <t>Self-Serve subscribers</t>
         </is>
       </c>
-      <c r="D126" s="51" t="n">
+      <c r="D126" s="52" t="n">
         <v>1127900</v>
       </c>
-      <c r="E126" s="52">
+      <c r="E126" s="53">
         <f>'Business case'!B5</f>
         <v/>
       </c>
-      <c r="F126" s="53">
+      <c r="F126" s="54">
         <f>IF(AND(ISNUMBER(D126),ISNUMBER(E126)),E126-D126,"")</f>
         <v/>
       </c>
@@ -4442,14 +5075,14 @@
           <t>Self-Serve ARPU</t>
         </is>
       </c>
-      <c r="D127" s="51" t="n">
+      <c r="D127" s="52" t="n">
         <v>204</v>
       </c>
-      <c r="E127" s="52">
+      <c r="E127" s="53">
         <f>'Business case'!B6</f>
         <v/>
       </c>
-      <c r="F127" s="53">
+      <c r="F127" s="54">
         <f>IF(AND(ISNUMBER(D127),ISNUMBER(E127)),E127-D127,"")</f>
         <v/>
       </c>
@@ -4469,14 +5102,14 @@
           <t>Enterprise ARPU</t>
         </is>
       </c>
-      <c r="D128" s="51" t="n">
+      <c r="D128" s="52" t="n">
         <v>24567</v>
       </c>
-      <c r="E128" s="52">
+      <c r="E128" s="53">
         <f>'Business case'!B7</f>
         <v/>
       </c>
-      <c r="F128" s="53">
+      <c r="F128" s="54">
         <f>IF(AND(ISNUMBER(D128),ISNUMBER(E128)),E128-D128,"")</f>
         <v/>
       </c>
@@ -4496,14 +5129,14 @@
           <t>Eligible accounts</t>
         </is>
       </c>
-      <c r="D129" s="51" t="n">
+      <c r="D129" s="52" t="n">
         <v>22558</v>
       </c>
-      <c r="E129" s="52">
+      <c r="E129" s="53">
         <f>'Business case'!B10</f>
         <v/>
       </c>
-      <c r="F129" s="53">
+      <c r="F129" s="54">
         <f>IF(AND(ISNUMBER(D129),ISNUMBER(E129)),E129-D129,"")</f>
         <v/>
       </c>
@@ -4523,14 +5156,14 @@
           <t>Upgrades per year</t>
         </is>
       </c>
-      <c r="D130" s="51" t="n">
+      <c r="D130" s="52" t="n">
         <v>225.58</v>
       </c>
-      <c r="E130" s="52">
+      <c r="E130" s="53">
         <f>'Business case'!B11</f>
         <v/>
       </c>
-      <c r="F130" s="53">
+      <c r="F130" s="54">
         <f>IF(AND(ISNUMBER(D130),ISNUMBER(E130)),E130-D130,"")</f>
         <v/>
       </c>
@@ -4550,14 +5183,14 @@
           <t>First-year contract value</t>
         </is>
       </c>
-      <c r="D131" s="51" t="n">
+      <c r="D131" s="52" t="n">
         <v>12283.5</v>
       </c>
-      <c r="E131" s="52">
+      <c r="E131" s="53">
         <f>'Business case'!B12</f>
         <v/>
       </c>
-      <c r="F131" s="53">
+      <c r="F131" s="54">
         <f>IF(AND(ISNUMBER(D131),ISNUMBER(E131)),E131-D131,"")</f>
         <v/>
       </c>
@@ -4577,14 +5210,14 @@
           <t>Year 1 enterprise_revenue</t>
         </is>
       </c>
-      <c r="D132" s="51" t="n">
+      <c r="D132" s="52" t="n">
         <v>1385455.965</v>
       </c>
-      <c r="E132" s="52">
+      <c r="E132" s="53">
         <f>'Business case'!B18</f>
         <v/>
       </c>
-      <c r="F132" s="53">
+      <c r="F132" s="54">
         <f>IF(AND(ISNUMBER(D132),ISNUMBER(E132)),E132-D132,"")</f>
         <v/>
       </c>
@@ -4604,14 +5237,14 @@
           <t>Year 1 cannibalised</t>
         </is>
       </c>
-      <c r="D133" s="51" t="n">
+      <c r="D133" s="52" t="n">
         <v>23009.16</v>
       </c>
-      <c r="E133" s="52">
+      <c r="E133" s="53">
         <f>'Business case'!B19</f>
         <v/>
       </c>
-      <c r="F133" s="53">
+      <c r="F133" s="54">
         <f>IF(AND(ISNUMBER(D133),ISNUMBER(E133)),E133-D133,"")</f>
         <v/>
       </c>
@@ -4631,14 +5264,14 @@
           <t>Year 1 net_revenue</t>
         </is>
       </c>
-      <c r="D134" s="51" t="n">
+      <c r="D134" s="52" t="n">
         <v>1362446.805</v>
       </c>
-      <c r="E134" s="52">
+      <c r="E134" s="53">
         <f>'Business case'!B20</f>
         <v/>
       </c>
-      <c r="F134" s="53">
+      <c r="F134" s="54">
         <f>IF(AND(ISNUMBER(D134),ISNUMBER(E134)),E134-D134,"")</f>
         <v/>
       </c>
@@ -4658,14 +5291,14 @@
           <t>Year 1 gross_profit</t>
         </is>
       </c>
-      <c r="D135" s="51" t="n">
+      <c r="D135" s="52" t="n">
         <v>1062708.5079</v>
       </c>
-      <c r="E135" s="52">
+      <c r="E135" s="53">
         <f>'Business case'!B21</f>
         <v/>
       </c>
-      <c r="F135" s="53">
+      <c r="F135" s="54">
         <f>IF(AND(ISNUMBER(D135),ISNUMBER(E135)),E135-D135,"")</f>
         <v/>
       </c>
@@ -4685,14 +5318,14 @@
           <t>Year 1 sales_cost</t>
         </is>
       </c>
-      <c r="D136" s="51" t="n">
+      <c r="D136" s="52" t="n">
         <v>1080000</v>
       </c>
-      <c r="E136" s="52">
+      <c r="E136" s="53">
         <f>'Business case'!B22</f>
         <v/>
       </c>
-      <c r="F136" s="53">
+      <c r="F136" s="54">
         <f>IF(AND(ISNUMBER(D136),ISNUMBER(E136)),E136-D136,"")</f>
         <v/>
       </c>
@@ -4712,14 +5345,14 @@
           <t>Year 1 outreach_cost</t>
         </is>
       </c>
-      <c r="D137" s="51" t="n">
+      <c r="D137" s="52" t="n">
         <v>676740</v>
       </c>
-      <c r="E137" s="52">
+      <c r="E137" s="53">
         <f>'Business case'!B23</f>
         <v/>
       </c>
-      <c r="F137" s="53">
+      <c r="F137" s="54">
         <f>IF(AND(ISNUMBER(D137),ISNUMBER(E137)),E137-D137,"")</f>
         <v/>
       </c>
@@ -4739,14 +5372,14 @@
           <t>Year 1 contribution</t>
         </is>
       </c>
-      <c r="D138" s="51" t="n">
+      <c r="D138" s="52" t="n">
         <v>-1094031.4921</v>
       </c>
-      <c r="E138" s="52">
+      <c r="E138" s="53">
         <f>'Business case'!B25</f>
         <v/>
       </c>
-      <c r="F138" s="53">
+      <c r="F138" s="54">
         <f>IF(AND(ISNUMBER(D138),ISNUMBER(E138)),E138-D138,"")</f>
         <v/>
       </c>
@@ -4766,14 +5399,14 @@
           <t>Year 1 present_value</t>
         </is>
       </c>
-      <c r="D139" s="51" t="n">
+      <c r="D139" s="52" t="n">
         <v>-994574.0837272726</v>
       </c>
-      <c r="E139" s="52">
+      <c r="E139" s="53">
         <f>'Business case'!B28</f>
         <v/>
       </c>
-      <c r="F139" s="53">
+      <c r="F139" s="54">
         <f>IF(AND(ISNUMBER(D139),ISNUMBER(E139)),E139-D139,"")</f>
         <v/>
       </c>
@@ -4793,14 +5426,14 @@
           <t>Year 2 enterprise_revenue</t>
         </is>
       </c>
-      <c r="D140" s="51" t="n">
+      <c r="D140" s="52" t="n">
         <v>3879276.702</v>
       </c>
-      <c r="E140" s="52">
+      <c r="E140" s="53">
         <f>'Business case'!C18</f>
         <v/>
       </c>
-      <c r="F140" s="53">
+      <c r="F140" s="54">
         <f>IF(AND(ISNUMBER(D140),ISNUMBER(E140)),E140-D140,"")</f>
         <v/>
       </c>
@@ -4820,14 +5453,14 @@
           <t>Year 2 cannibalised</t>
         </is>
       </c>
-      <c r="D141" s="51" t="n">
+      <c r="D141" s="52" t="n">
         <v>69027.48</v>
       </c>
-      <c r="E141" s="52">
+      <c r="E141" s="53">
         <f>'Business case'!C19</f>
         <v/>
       </c>
-      <c r="F141" s="53">
+      <c r="F141" s="54">
         <f>IF(AND(ISNUMBER(D141),ISNUMBER(E141)),E141-D141,"")</f>
         <v/>
       </c>
@@ -4847,14 +5480,14 @@
           <t>Year 2 net_revenue</t>
         </is>
       </c>
-      <c r="D142" s="51" t="n">
+      <c r="D142" s="52" t="n">
         <v>3810249.222</v>
       </c>
-      <c r="E142" s="52">
+      <c r="E142" s="53">
         <f>'Business case'!C20</f>
         <v/>
       </c>
-      <c r="F142" s="53">
+      <c r="F142" s="54">
         <f>IF(AND(ISNUMBER(D142),ISNUMBER(E142)),E142-D142,"")</f>
         <v/>
       </c>
@@ -4874,14 +5507,14 @@
           <t>Year 2 gross_profit</t>
         </is>
       </c>
-      <c r="D143" s="51" t="n">
+      <c r="D143" s="52" t="n">
         <v>2971994.39316</v>
       </c>
-      <c r="E143" s="52">
+      <c r="E143" s="53">
         <f>'Business case'!C21</f>
         <v/>
       </c>
-      <c r="F143" s="53">
+      <c r="F143" s="54">
         <f>IF(AND(ISNUMBER(D143),ISNUMBER(E143)),E143-D143,"")</f>
         <v/>
       </c>
@@ -4901,14 +5534,14 @@
           <t>Year 2 sales_cost</t>
         </is>
       </c>
-      <c r="D144" s="51" t="n">
+      <c r="D144" s="52" t="n">
         <v>1080000</v>
       </c>
-      <c r="E144" s="52">
+      <c r="E144" s="53">
         <f>'Business case'!C22</f>
         <v/>
       </c>
-      <c r="F144" s="53">
+      <c r="F144" s="54">
         <f>IF(AND(ISNUMBER(D144),ISNUMBER(E144)),E144-D144,"")</f>
         <v/>
       </c>
@@ -4928,14 +5561,14 @@
           <t>Year 2 outreach_cost</t>
         </is>
       </c>
-      <c r="D145" s="51" t="n">
+      <c r="D145" s="52" t="n">
         <v>676740</v>
       </c>
-      <c r="E145" s="52">
+      <c r="E145" s="53">
         <f>'Business case'!C23</f>
         <v/>
       </c>
-      <c r="F145" s="53">
+      <c r="F145" s="54">
         <f>IF(AND(ISNUMBER(D145),ISNUMBER(E145)),E145-D145,"")</f>
         <v/>
       </c>
@@ -4955,14 +5588,14 @@
           <t>Year 2 contribution</t>
         </is>
       </c>
-      <c r="D146" s="51" t="n">
+      <c r="D146" s="52" t="n">
         <v>1215254.39316</v>
       </c>
-      <c r="E146" s="52">
+      <c r="E146" s="53">
         <f>'Business case'!C25</f>
         <v/>
       </c>
-      <c r="F146" s="53">
+      <c r="F146" s="54">
         <f>IF(AND(ISNUMBER(D146),ISNUMBER(E146)),E146-D146,"")</f>
         <v/>
       </c>
@@ -4982,14 +5615,14 @@
           <t>Year 2 present_value</t>
         </is>
       </c>
-      <c r="D147" s="51" t="n">
+      <c r="D147" s="52" t="n">
         <v>1004342.47368595</v>
       </c>
-      <c r="E147" s="52">
+      <c r="E147" s="53">
         <f>'Business case'!C28</f>
         <v/>
       </c>
-      <c r="F147" s="53">
+      <c r="F147" s="54">
         <f>IF(AND(ISNUMBER(D147),ISNUMBER(E147)),E147-D147,"")</f>
         <v/>
       </c>
@@ -5009,14 +5642,14 @@
           <t>Year 3 enterprise_revenue</t>
         </is>
       </c>
-      <c r="D148" s="51" t="n">
+      <c r="D148" s="52" t="n">
         <v>6123715.365300001</v>
       </c>
-      <c r="E148" s="52">
+      <c r="E148" s="53">
         <f>'Business case'!D18</f>
         <v/>
       </c>
-      <c r="F148" s="53">
+      <c r="F148" s="54">
         <f>IF(AND(ISNUMBER(D148),ISNUMBER(E148)),E148-D148,"")</f>
         <v/>
       </c>
@@ -5036,14 +5669,14 @@
           <t>Year 3 cannibalised</t>
         </is>
       </c>
-      <c r="D149" s="51" t="n">
+      <c r="D149" s="52" t="n">
         <v>115045.8</v>
       </c>
-      <c r="E149" s="52">
+      <c r="E149" s="53">
         <f>'Business case'!D19</f>
         <v/>
       </c>
-      <c r="F149" s="53">
+      <c r="F149" s="54">
         <f>IF(AND(ISNUMBER(D149),ISNUMBER(E149)),E149-D149,"")</f>
         <v/>
       </c>
@@ -5063,14 +5696,14 @@
           <t>Year 3 net_revenue</t>
         </is>
       </c>
-      <c r="D150" s="51" t="n">
+      <c r="D150" s="52" t="n">
         <v>6008669.565300001</v>
       </c>
-      <c r="E150" s="52">
+      <c r="E150" s="53">
         <f>'Business case'!D20</f>
         <v/>
       </c>
-      <c r="F150" s="53">
+      <c r="F150" s="54">
         <f>IF(AND(ISNUMBER(D150),ISNUMBER(E150)),E150-D150,"")</f>
         <v/>
       </c>
@@ -5090,14 +5723,14 @@
           <t>Year 3 gross_profit</t>
         </is>
       </c>
-      <c r="D151" s="51" t="n">
+      <c r="D151" s="52" t="n">
         <v>4686762.260934001</v>
       </c>
-      <c r="E151" s="52">
+      <c r="E151" s="53">
         <f>'Business case'!D21</f>
         <v/>
       </c>
-      <c r="F151" s="53">
+      <c r="F151" s="54">
         <f>IF(AND(ISNUMBER(D151),ISNUMBER(E151)),E151-D151,"")</f>
         <v/>
       </c>
@@ -5117,14 +5750,14 @@
           <t>Year 3 sales_cost</t>
         </is>
       </c>
-      <c r="D152" s="51" t="n">
+      <c r="D152" s="52" t="n">
         <v>1080000</v>
       </c>
-      <c r="E152" s="52">
+      <c r="E152" s="53">
         <f>'Business case'!D22</f>
         <v/>
       </c>
-      <c r="F152" s="53">
+      <c r="F152" s="54">
         <f>IF(AND(ISNUMBER(D152),ISNUMBER(E152)),E152-D152,"")</f>
         <v/>
       </c>
@@ -5144,14 +5777,14 @@
           <t>Year 3 outreach_cost</t>
         </is>
       </c>
-      <c r="D153" s="51" t="n">
+      <c r="D153" s="52" t="n">
         <v>676740</v>
       </c>
-      <c r="E153" s="52">
+      <c r="E153" s="53">
         <f>'Business case'!D23</f>
         <v/>
       </c>
-      <c r="F153" s="53">
+      <c r="F153" s="54">
         <f>IF(AND(ISNUMBER(D153),ISNUMBER(E153)),E153-D153,"")</f>
         <v/>
       </c>
@@ -5171,14 +5804,14 @@
           <t>Year 3 contribution</t>
         </is>
       </c>
-      <c r="D154" s="51" t="n">
+      <c r="D154" s="52" t="n">
         <v>2930022.260934001</v>
       </c>
-      <c r="E154" s="52">
+      <c r="E154" s="53">
         <f>'Business case'!D25</f>
         <v/>
       </c>
-      <c r="F154" s="53">
+      <c r="F154" s="54">
         <f>IF(AND(ISNUMBER(D154),ISNUMBER(E154)),E154-D154,"")</f>
         <v/>
       </c>
@@ -5198,14 +5831,14 @@
           <t>Year 3 present_value</t>
         </is>
       </c>
-      <c r="D155" s="51" t="n">
+      <c r="D155" s="52" t="n">
         <v>2201369.091610819</v>
       </c>
-      <c r="E155" s="52">
+      <c r="E155" s="53">
         <f>'Business case'!D28</f>
         <v/>
       </c>
-      <c r="F155" s="53">
+      <c r="F155" s="54">
         <f>IF(AND(ISNUMBER(D155),ISNUMBER(E155)),E155-D155,"")</f>
         <v/>
       </c>
@@ -5225,14 +5858,14 @@
           <t>Net present value</t>
         </is>
       </c>
-      <c r="D156" s="51" t="n">
+      <c r="D156" s="52" t="n">
         <v>2211137.481569497</v>
       </c>
-      <c r="E156" s="52">
+      <c r="E156" s="53">
         <f>'Business case'!B30</f>
         <v/>
       </c>
-      <c r="F156" s="53">
+      <c r="F156" s="54">
         <f>IF(AND(ISNUMBER(D156),ISNUMBER(E156)),E156-D156,"")</f>
         <v/>
       </c>
@@ -5259,7 +5892,7 @@
         <f>'Business case'!B31</f>
         <v/>
       </c>
-      <c r="F157" s="53">
+      <c r="F157" s="54">
         <f>IF(AND(ISNUMBER(D157),ISNUMBER(E157)),E157-D157,"")</f>
         <v/>
       </c>
@@ -5279,14 +5912,14 @@
           <t>Break-even uplift (closed form vs bisection)</t>
         </is>
       </c>
-      <c r="D158" s="51" t="n">
+      <c r="D158" s="52" t="n">
         <v>0.006815540959870341</v>
       </c>
-      <c r="E158" s="52">
+      <c r="E158" s="53">
         <f>'Business case'!B37</f>
         <v/>
       </c>
-      <c r="F158" s="53">
+      <c r="F158" s="54">
         <f>IF(AND(ISNUMBER(D158),ISNUMBER(E158)),E158-D158,"")</f>
         <v/>
       </c>
@@ -5306,14 +5939,14 @@
           <t>uplift low</t>
         </is>
       </c>
-      <c r="D159" s="51" t="n">
+      <c r="D159" s="52" t="n">
         <v>-1954978.245538994</v>
       </c>
-      <c r="E159" s="52">
+      <c r="E159" s="53">
         <f>Sensitivity!T5</f>
         <v/>
       </c>
-      <c r="F159" s="53">
+      <c r="F159" s="54">
         <f>IF(AND(ISNUMBER(D159),ISNUMBER(E159)),E159-D159,"")</f>
         <v/>
       </c>
@@ -5333,14 +5966,14 @@
           <t>uplift high</t>
         </is>
       </c>
-      <c r="D160" s="51" t="n">
+      <c r="D160" s="52" t="n">
         <v>9154663.693416979</v>
       </c>
-      <c r="E160" s="52">
+      <c r="E160" s="53">
         <f>Sensitivity!T6</f>
         <v/>
       </c>
-      <c r="F160" s="53">
+      <c r="F160" s="54">
         <f>IF(AND(ISNUMBER(D160),ISNUMBER(E160)),E160-D160,"")</f>
         <v/>
       </c>
@@ -5360,14 +5993,14 @@
           <t>entry_acv_share low</t>
         </is>
       </c>
-      <c r="D161" s="51" t="n">
+      <c r="D161" s="52" t="n">
         <v>-617565.9699758076</v>
       </c>
-      <c r="E161" s="52">
+      <c r="E161" s="53">
         <f>Sensitivity!T7</f>
         <v/>
       </c>
-      <c r="F161" s="53">
+      <c r="F161" s="54">
         <f>IF(AND(ISNUMBER(D161),ISNUMBER(E161)),E161-D161,"")</f>
         <v/>
       </c>
@@ -5387,14 +6020,14 @@
           <t>entry_acv_share high</t>
         </is>
       </c>
-      <c r="D162" s="51" t="n">
+      <c r="D162" s="52" t="n">
         <v>5039840.933114798</v>
       </c>
-      <c r="E162" s="52">
+      <c r="E162" s="53">
         <f>Sensitivity!T8</f>
         <v/>
       </c>
-      <c r="F162" s="53">
+      <c r="F162" s="54">
         <f>IF(AND(ISNUMBER(D162),ISNUMBER(E162)),E162-D162,"")</f>
         <v/>
       </c>
@@ -5414,14 +6047,14 @@
           <t>eligible_share low</t>
         </is>
       </c>
-      <c r="D163" s="51" t="n">
+      <c r="D163" s="52" t="n">
         <v>923750.5589665666</v>
       </c>
-      <c r="E163" s="52">
+      <c r="E163" s="53">
         <f>Sensitivity!T9</f>
         <v/>
       </c>
-      <c r="F163" s="53">
+      <c r="F163" s="54">
         <f>IF(AND(ISNUMBER(D163),ISNUMBER(E163)),E163-D163,"")</f>
         <v/>
       </c>
@@ -5441,14 +6074,14 @@
           <t>eligible_share high</t>
         </is>
       </c>
-      <c r="D164" s="51" t="n">
+      <c r="D164" s="52" t="n">
         <v>4785911.326775357</v>
       </c>
-      <c r="E164" s="52">
+      <c r="E164" s="53">
         <f>Sensitivity!T10</f>
         <v/>
       </c>
-      <c r="F164" s="53">
+      <c r="F164" s="54">
         <f>IF(AND(ISNUMBER(D164),ISNUMBER(E164)),E164-D164,"")</f>
         <v/>
       </c>
@@ -5468,14 +6101,14 @@
           <t>upgrades_per_ae low</t>
         </is>
       </c>
-      <c r="D165" s="51" t="n">
+      <c r="D165" s="52" t="n">
         <v>-474662.6686934633</v>
       </c>
-      <c r="E165" s="52">
+      <c r="E165" s="53">
         <f>Sensitivity!T11</f>
         <v/>
       </c>
-      <c r="F165" s="53">
+      <c r="F165" s="54">
         <f>IF(AND(ISNUMBER(D165),ISNUMBER(E165)),E165-D165,"")</f>
         <v/>
       </c>
@@ -5495,14 +6128,14 @@
           <t>upgrades_per_ae high</t>
         </is>
       </c>
-      <c r="D166" s="51" t="n">
+      <c r="D166" s="52" t="n">
         <v>3106404.198323816</v>
       </c>
-      <c r="E166" s="52">
+      <c r="E166" s="53">
         <f>Sensitivity!T12</f>
         <v/>
       </c>
-      <c r="F166" s="53">
+      <c r="F166" s="54">
         <f>IF(AND(ISNUMBER(D166),ISNUMBER(E166)),E166-D166,"")</f>
         <v/>
       </c>
@@ -5522,14 +6155,14 @@
           <t>outreach_cost low</t>
         </is>
       </c>
-      <c r="D167" s="51" t="n">
+      <c r="D167" s="52" t="n">
         <v>3052613.589758828</v>
       </c>
-      <c r="E167" s="52">
+      <c r="E167" s="53">
         <f>Sensitivity!T13</f>
         <v/>
       </c>
-      <c r="F167" s="53">
+      <c r="F167" s="54">
         <f>IF(AND(ISNUMBER(D167),ISNUMBER(E167)),E167-D167,"")</f>
         <v/>
       </c>
@@ -5549,14 +6182,14 @@
           <t>outreach_cost high</t>
         </is>
       </c>
-      <c r="D168" s="51" t="n">
+      <c r="D168" s="52" t="n">
         <v>528185.2651908342</v>
       </c>
-      <c r="E168" s="52">
+      <c r="E168" s="53">
         <f>Sensitivity!T14</f>
         <v/>
       </c>
-      <c r="F168" s="53">
+      <c r="F168" s="54">
         <f>IF(AND(ISNUMBER(D168),ISNUMBER(E168)),E168-D168,"")</f>
         <v/>
       </c>
@@ -5576,14 +6209,14 @@
           <t>retention low</t>
         </is>
       </c>
-      <c r="D169" s="51" t="n">
+      <c r="D169" s="52" t="n">
         <v>1297735.821699098</v>
       </c>
-      <c r="E169" s="52">
+      <c r="E169" s="53">
         <f>Sensitivity!T15</f>
         <v/>
       </c>
-      <c r="F169" s="53">
+      <c r="F169" s="54">
         <f>IF(AND(ISNUMBER(D169),ISNUMBER(E169)),E169-D169,"")</f>
         <v/>
       </c>
@@ -5603,14 +6236,14 @@
           <t>retention high</t>
         </is>
       </c>
-      <c r="D170" s="51" t="n">
+      <c r="D170" s="52" t="n">
         <v>3197611.274229526</v>
       </c>
-      <c r="E170" s="52">
+      <c r="E170" s="53">
         <f>Sensitivity!T16</f>
         <v/>
       </c>
-      <c r="F170" s="53">
+      <c r="F170" s="54">
         <f>IF(AND(ISNUMBER(D170),ISNUMBER(E170)),E170-D170,"")</f>
         <v/>
       </c>
@@ -5630,14 +6263,14 @@
           <t>gross_margin low</t>
         </is>
       </c>
-      <c r="D171" s="51" t="n">
+      <c r="D171" s="52" t="n">
         <v>1498980.947021036</v>
       </c>
-      <c r="E171" s="52">
+      <c r="E171" s="53">
         <f>Sensitivity!T17</f>
         <v/>
       </c>
-      <c r="F171" s="53">
+      <c r="F171" s="54">
         <f>IF(AND(ISNUMBER(D171),ISNUMBER(E171)),E171-D171,"")</f>
         <v/>
       </c>
@@ -5657,14 +6290,14 @@
           <t>gross_margin high</t>
         </is>
       </c>
-      <c r="D172" s="51" t="n">
+      <c r="D172" s="52" t="n">
         <v>2567215.748843726</v>
       </c>
-      <c r="E172" s="52">
+      <c r="E172" s="53">
         <f>Sensitivity!T18</f>
         <v/>
       </c>
-      <c r="F172" s="53">
+      <c r="F172" s="54">
         <f>IF(AND(ISNUMBER(D172),ISNUMBER(E172)),E172-D172,"")</f>
         <v/>
       </c>
@@ -5691,7 +6324,7 @@
         <f>'Test design'!I5</f>
         <v/>
       </c>
-      <c r="F173" s="53">
+      <c r="F173" s="54">
         <f>IF(AND(ISNUMBER(D173),ISNUMBER(E173)),E173-D173,"")</f>
         <v/>
       </c>
@@ -5720,7 +6353,7 @@
         <f>'Test design'!L5</f>
         <v/>
       </c>
-      <c r="F174" s="53">
+      <c r="F174" s="54">
         <f>IF(AND(ISNUMBER(D174),ISNUMBER(E174)),E174-D174,"")</f>
         <v/>
       </c>
@@ -5747,7 +6380,7 @@
         <f>'Test design'!I6</f>
         <v/>
       </c>
-      <c r="F175" s="53">
+      <c r="F175" s="54">
         <f>IF(AND(ISNUMBER(D175),ISNUMBER(E175)),E175-D175,"")</f>
         <v/>
       </c>
@@ -5776,7 +6409,7 @@
         <f>'Test design'!L6</f>
         <v/>
       </c>
-      <c r="F176" s="53">
+      <c r="F176" s="54">
         <f>IF(AND(ISNUMBER(D176),ISNUMBER(E176)),E176-D176,"")</f>
         <v/>
       </c>
@@ -5803,7 +6436,7 @@
         <f>'Test design'!I7</f>
         <v/>
       </c>
-      <c r="F177" s="53">
+      <c r="F177" s="54">
         <f>IF(AND(ISNUMBER(D177),ISNUMBER(E177)),E177-D177,"")</f>
         <v/>
       </c>
@@ -5832,7 +6465,7 @@
         <f>'Test design'!L7</f>
         <v/>
       </c>
-      <c r="F178" s="53">
+      <c r="F178" s="54">
         <f>IF(AND(ISNUMBER(D178),ISNUMBER(E178)),E178-D178,"")</f>
         <v/>
       </c>
@@ -5859,7 +6492,7 @@
         <f>'Test design'!I8</f>
         <v/>
       </c>
-      <c r="F179" s="53">
+      <c r="F179" s="54">
         <f>IF(AND(ISNUMBER(D179),ISNUMBER(E179)),E179-D179,"")</f>
         <v/>
       </c>
@@ -5888,7 +6521,7 @@
         <f>'Test design'!L8</f>
         <v/>
       </c>
-      <c r="F180" s="53">
+      <c r="F180" s="54">
         <f>IF(AND(ISNUMBER(D180),ISNUMBER(E180)),E180-D180,"")</f>
         <v/>
       </c>
@@ -5908,14 +6541,14 @@
           <t>Upgrade rate, control</t>
         </is>
       </c>
-      <c r="D181" s="51" t="n">
+      <c r="D181" s="52" t="n">
         <v>0.008122099250267762</v>
       </c>
-      <c r="E181" s="52">
+      <c r="E181" s="53">
         <f>'Test readout'!B10</f>
         <v/>
       </c>
-      <c r="F181" s="53">
+      <c r="F181" s="54">
         <f>IF(AND(ISNUMBER(D181),ISNUMBER(E181)),E181-D181,"")</f>
         <v/>
       </c>
@@ -5935,14 +6568,14 @@
           <t>Upgrade rate, treatment</t>
         </is>
       </c>
-      <c r="D182" s="51" t="n">
+      <c r="D182" s="52" t="n">
         <v>0.01171393341553638</v>
       </c>
-      <c r="E182" s="52">
+      <c r="E182" s="53">
         <f>'Test readout'!B11</f>
         <v/>
       </c>
-      <c r="F182" s="53">
+      <c r="F182" s="54">
         <f>IF(AND(ISNUMBER(D182),ISNUMBER(E182)),E182-D182,"")</f>
         <v/>
       </c>
@@ -5962,14 +6595,14 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="D183" s="51" t="n">
+      <c r="D183" s="52" t="n">
         <v>0.003591834165268613</v>
       </c>
-      <c r="E183" s="52">
+      <c r="E183" s="53">
         <f>'Test readout'!B12</f>
         <v/>
       </c>
-      <c r="F183" s="53">
+      <c r="F183" s="54">
         <f>IF(AND(ISNUMBER(D183),ISNUMBER(E183)),E183-D183,"")</f>
         <v/>
       </c>
@@ -5989,14 +6622,14 @@
           <t>Standard error</t>
         </is>
       </c>
-      <c r="D184" s="51" t="n">
+      <c r="D184" s="52" t="n">
         <v>0.001318581182365817</v>
       </c>
-      <c r="E184" s="52">
+      <c r="E184" s="53">
         <f>'Test readout'!B13</f>
         <v/>
       </c>
-      <c r="F184" s="53">
+      <c r="F184" s="54">
         <f>IF(AND(ISNUMBER(D184),ISNUMBER(E184)),E184-D184,"")</f>
         <v/>
       </c>
@@ -6016,14 +6649,14 @@
           <t>One-sided 95% lower bound</t>
         </is>
       </c>
-      <c r="D185" s="51" t="n">
+      <c r="D185" s="52" t="n">
         <v>0.00142296112502424</v>
       </c>
-      <c r="E185" s="52">
+      <c r="E185" s="53">
         <f>'Test readout'!B14</f>
         <v/>
       </c>
-      <c r="F185" s="53">
+      <c r="F185" s="54">
         <f>IF(AND(ISNUMBER(D185),ISNUMBER(E185)),E185-D185,"")</f>
         <v/>
       </c>
@@ -6043,14 +6676,14 @@
           <t>Break-even difference in the window</t>
         </is>
       </c>
-      <c r="D186" s="51" t="n">
+      <c r="D186" s="52" t="n">
         <v>0.003361088692538798</v>
       </c>
-      <c r="E186" s="52">
+      <c r="E186" s="53">
         <f>'Test readout'!B15</f>
         <v/>
       </c>
-      <c r="F186" s="53">
+      <c r="F186" s="54">
         <f>IF(AND(ISNUMBER(D186),ISNUMBER(E186)),E186-D186,"")</f>
         <v/>
       </c>
@@ -6070,14 +6703,14 @@
           <t>Uplift per year, estimate</t>
         </is>
       </c>
-      <c r="D187" s="51" t="n">
+      <c r="D187" s="52" t="n">
         <v>0.007283441501794687</v>
       </c>
-      <c r="E187" s="52">
+      <c r="E187" s="53">
         <f>'Test readout'!B16</f>
         <v/>
       </c>
-      <c r="F187" s="53">
+      <c r="F187" s="54">
         <f>IF(AND(ISNUMBER(D187),ISNUMBER(E187)),E187-D187,"")</f>
         <v/>
       </c>
@@ -6097,14 +6730,14 @@
           <t>Sample ratio check, p-value</t>
         </is>
       </c>
-      <c r="D188" s="51" t="n">
+      <c r="D188" s="52" t="n">
         <v>0.3179334517142656</v>
       </c>
-      <c r="E188" s="52">
+      <c r="E188" s="53">
         <f>'Test readout'!B17</f>
         <v/>
       </c>
-      <c r="F188" s="53">
+      <c r="F188" s="54">
         <f>IF(AND(ISNUMBER(D188),ISNUMBER(E188)),E188-D188,"")</f>
         <v/>
       </c>
@@ -6124,14 +6757,14 @@
           <t>Cancellations, difference</t>
         </is>
       </c>
-      <c r="D189" s="51" t="n">
+      <c r="D189" s="52" t="n">
         <v>-0.002189792681430554</v>
       </c>
-      <c r="E189" s="52">
+      <c r="E189" s="53">
         <f>'Test readout'!B18</f>
         <v/>
       </c>
-      <c r="F189" s="53">
+      <c r="F189" s="54">
         <f>IF(AND(ISNUMBER(D189),ISNUMBER(E189)),E189-D189,"")</f>
         <v/>
       </c>
@@ -6151,14 +6784,14 @@
           <t>Cancellations, upper bound</t>
         </is>
       </c>
-      <c r="D190" s="51" t="n">
+      <c r="D190" s="52" t="n">
         <v>0.002929921397394245</v>
       </c>
-      <c r="E190" s="52">
+      <c r="E190" s="53">
         <f>'Test readout'!B19</f>
         <v/>
       </c>
-      <c r="F190" s="53">
+      <c r="F190" s="54">
         <f>IF(AND(ISNUMBER(D190),ISNUMBER(E190)),E190-D190,"")</f>
         <v/>
       </c>
@@ -6187,7 +6820,7 @@
         <f>'Test readout'!B22</f>
         <v/>
       </c>
-      <c r="F191" s="53">
+      <c r="F191" s="54">
         <f>IF(AND(ISNUMBER(D191),ISNUMBER(E191)),E191-D191,"")</f>
         <v/>
       </c>
@@ -6199,24 +6832,22 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Value of test</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Smallest feasible test</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>180 days, one-sided</t>
-        </is>
-      </c>
-      <c r="E192" s="6">
-        <f>Summary!B10</f>
-        <v/>
-      </c>
-      <c r="F192" s="53">
+          <t>Cost of the test</t>
+        </is>
+      </c>
+      <c r="D192" s="52" t="n">
+        <v>655634.5205479452</v>
+      </c>
+      <c r="E192" s="53">
+        <f>'Value of test'!B5</f>
+        <v/>
+      </c>
+      <c r="F192" s="54">
         <f>IF(AND(ISNUMBER(D192),ISNUMBER(E192)),E192-D192,"")</f>
         <v/>
       </c>
@@ -6225,8 +6856,635 @@
         <v/>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>NPV at 0.000</t>
+        </is>
+      </c>
+      <c r="D193" s="52" t="n">
+        <v>-4732388.730277985</v>
+      </c>
+      <c r="E193" s="53">
+        <f>'Value of test'!D9</f>
+        <v/>
+      </c>
+      <c r="F193" s="54">
+        <f>IF(AND(ISNUMBER(D193),ISNUMBER(E193)),E193-D193,"")</f>
+        <v/>
+      </c>
+      <c r="G193" s="5">
+        <f>IF(AND(D193="",E193=""),"Yes",IF(AND(ISNUMBER(D193),ISNUMBER(E193)),IF(ABS(E193-D193)&lt;=1E-6*MAX(1,ABS(D193)),"Yes","No"),IF(D193=E193,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>Test-first value at 0.000</t>
+        </is>
+      </c>
+      <c r="D194" s="52" t="n">
+        <v>-655634.5205479452</v>
+      </c>
+      <c r="E194" s="53">
+        <f>'Value of test'!G9</f>
+        <v/>
+      </c>
+      <c r="F194" s="54">
+        <f>IF(AND(ISNUMBER(D194),ISNUMBER(E194)),E194-D194,"")</f>
+        <v/>
+      </c>
+      <c r="G194" s="5">
+        <f>IF(AND(D194="",E194=""),"Yes",IF(AND(ISNUMBER(D194),ISNUMBER(E194)),IF(ABS(E194-D194)&lt;=1E-6*MAX(1,ABS(D194)),"Yes","No"),IF(D194=E194,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>NPV at 0.004</t>
+        </is>
+      </c>
+      <c r="D195" s="52" t="n">
+        <v>-1954978.245538994</v>
+      </c>
+      <c r="E195" s="53">
+        <f>'Value of test'!D10</f>
+        <v/>
+      </c>
+      <c r="F195" s="54">
+        <f>IF(AND(ISNUMBER(D195),ISNUMBER(E195)),E195-D195,"")</f>
+        <v/>
+      </c>
+      <c r="G195" s="5">
+        <f>IF(AND(D195="",E195=""),"Yes",IF(AND(ISNUMBER(D195),ISNUMBER(E195)),IF(ABS(E195-D195)&lt;=1E-6*MAX(1,ABS(D195)),"Yes","No"),IF(D195=E195,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Test-first value at 0.004</t>
+        </is>
+      </c>
+      <c r="D196" s="52" t="n">
+        <v>-863132.2094457432</v>
+      </c>
+      <c r="E196" s="53">
+        <f>'Value of test'!G10</f>
+        <v/>
+      </c>
+      <c r="F196" s="54">
+        <f>IF(AND(ISNUMBER(D196),ISNUMBER(E196)),E196-D196,"")</f>
+        <v/>
+      </c>
+      <c r="G196" s="5">
+        <f>IF(AND(D196="",E196=""),"Yes",IF(AND(ISNUMBER(D196),ISNUMBER(E196)),IF(ABS(E196-D196)&lt;=1E-6*MAX(1,ABS(D196)),"Yes","No"),IF(D196=E196,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>NPV at 0.007</t>
+        </is>
+      </c>
+      <c r="D197" s="52" t="n">
+        <v>128079.6180152516</v>
+      </c>
+      <c r="E197" s="53">
+        <f>'Value of test'!D11</f>
+        <v/>
+      </c>
+      <c r="F197" s="54">
+        <f>IF(AND(ISNUMBER(D197),ISNUMBER(E197)),E197-D197,"")</f>
+        <v/>
+      </c>
+      <c r="G197" s="5">
+        <f>IF(AND(D197="",E197=""),"Yes",IF(AND(ISNUMBER(D197),ISNUMBER(E197)),IF(ABS(E197-D197)&lt;=1E-6*MAX(1,ABS(D197)),"Yes","No"),IF(D197=E197,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>Test-first value at 0.007</t>
+        </is>
+      </c>
+      <c r="D198" s="52" t="n">
+        <v>-394480.5042475903</v>
+      </c>
+      <c r="E198" s="53">
+        <f>'Value of test'!G11</f>
+        <v/>
+      </c>
+      <c r="F198" s="54">
+        <f>IF(AND(ISNUMBER(D198),ISNUMBER(E198)),E198-D198,"")</f>
+        <v/>
+      </c>
+      <c r="G198" s="5">
+        <f>IF(AND(D198="",E198=""),"Yes",IF(AND(ISNUMBER(D198),ISNUMBER(E198)),IF(ABS(E198-D198)&lt;=1E-6*MAX(1,ABS(D198)),"Yes","No"),IF(D198=E198,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>NPV at 0.010</t>
+        </is>
+      </c>
+      <c r="D199" s="52" t="n">
+        <v>2211137.481569497</v>
+      </c>
+      <c r="E199" s="53">
+        <f>'Value of test'!D12</f>
+        <v/>
+      </c>
+      <c r="F199" s="54">
+        <f>IF(AND(ISNUMBER(D199),ISNUMBER(E199)),E199-D199,"")</f>
+        <v/>
+      </c>
+      <c r="G199" s="5">
+        <f>IF(AND(D199="",E199=""),"Yes",IF(AND(ISNUMBER(D199),ISNUMBER(E199)),IF(ABS(E199-D199)&lt;=1E-6*MAX(1,ABS(D199)),"Yes","No"),IF(D199=E199,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Test-first value at 0.010</t>
+        </is>
+      </c>
+      <c r="D200" s="52" t="n">
+        <v>1366928.00544777</v>
+      </c>
+      <c r="E200" s="53">
+        <f>'Value of test'!G12</f>
+        <v/>
+      </c>
+      <c r="F200" s="54">
+        <f>IF(AND(ISNUMBER(D200),ISNUMBER(E200)),E200-D200,"")</f>
+        <v/>
+      </c>
+      <c r="G200" s="5">
+        <f>IF(AND(D200="",E200=""),"Yes",IF(AND(ISNUMBER(D200),ISNUMBER(E200)),IF(ABS(E200-D200)&lt;=1E-6*MAX(1,ABS(D200)),"Yes","No"),IF(D200=E200,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>NPV at 0.015</t>
+        </is>
+      </c>
+      <c r="D201" s="52" t="n">
+        <v>5682900.587493237</v>
+      </c>
+      <c r="E201" s="53">
+        <f>'Value of test'!D13</f>
+        <v/>
+      </c>
+      <c r="F201" s="54">
+        <f>IF(AND(ISNUMBER(D201),ISNUMBER(E201)),E201-D201,"")</f>
+        <v/>
+      </c>
+      <c r="G201" s="5">
+        <f>IF(AND(D201="",E201=""),"Yes",IF(AND(ISNUMBER(D201),ISNUMBER(E201)),IF(ABS(E201-D201)&lt;=1E-6*MAX(1,ABS(D201)),"Yes","No"),IF(D201=E201,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Test-first value at 0.015</t>
+        </is>
+      </c>
+      <c r="D202" s="52" t="n">
+        <v>4767142.334947645</v>
+      </c>
+      <c r="E202" s="53">
+        <f>'Value of test'!G13</f>
+        <v/>
+      </c>
+      <c r="F202" s="54">
+        <f>IF(AND(ISNUMBER(D202),ISNUMBER(E202)),E202-D202,"")</f>
+        <v/>
+      </c>
+      <c r="G202" s="5">
+        <f>IF(AND(D202="",E202=""),"Yes",IF(AND(ISNUMBER(D202),ISNUMBER(E202)),IF(ABS(E202-D202)&lt;=1E-6*MAX(1,ABS(D202)),"Yes","No"),IF(D202=E202,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>sceptical Launch now</t>
+        </is>
+      </c>
+      <c r="D203" s="52" t="n">
+        <v>-253814.3236363595</v>
+      </c>
+      <c r="E203" s="53">
+        <f>'Value of test'!B16</f>
+        <v/>
+      </c>
+      <c r="F203" s="54">
+        <f>IF(AND(ISNUMBER(D203),ISNUMBER(E203)),E203-D203,"")</f>
+        <v/>
+      </c>
+      <c r="G203" s="5">
+        <f>IF(AND(D203="",E203=""),"Yes",IF(AND(ISNUMBER(D203),ISNUMBER(E203)),IF(ABS(E203-D203)&lt;=1E-6*MAX(1,ABS(D203)),"Yes","No"),IF(D203=E203,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>optimistic Launch now</t>
+        </is>
+      </c>
+      <c r="D204" s="52" t="n">
+        <v>1725090.646740173</v>
+      </c>
+      <c r="E204" s="53">
+        <f>'Value of test'!C16</f>
+        <v/>
+      </c>
+      <c r="F204" s="54">
+        <f>IF(AND(ISNUMBER(D204),ISNUMBER(E204)),E204-D204,"")</f>
+        <v/>
+      </c>
+      <c r="G204" s="5">
+        <f>IF(AND(D204="",E204=""),"Yes",IF(AND(ISNUMBER(D204),ISNUMBER(E204)),IF(ABS(E204-D204)&lt;=1E-6*MAX(1,ABS(D204)),"Yes","No"),IF(D204=E204,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>sceptical Do nothing</t>
+        </is>
+      </c>
+      <c r="D205" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="53">
+        <f>'Value of test'!B17</f>
+        <v/>
+      </c>
+      <c r="F205" s="54">
+        <f>IF(AND(ISNUMBER(D205),ISNUMBER(E205)),E205-D205,"")</f>
+        <v/>
+      </c>
+      <c r="G205" s="5">
+        <f>IF(AND(D205="",E205=""),"Yes",IF(AND(ISNUMBER(D205),ISNUMBER(E205)),IF(ABS(E205-D205)&lt;=1E-6*MAX(1,ABS(D205)),"Yes","No"),IF(D205=E205,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>optimistic Do nothing</t>
+        </is>
+      </c>
+      <c r="D206" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" s="53">
+        <f>'Value of test'!C17</f>
+        <v/>
+      </c>
+      <c r="F206" s="54">
+        <f>IF(AND(ISNUMBER(D206),ISNUMBER(E206)),E206-D206,"")</f>
+        <v/>
+      </c>
+      <c r="G206" s="5">
+        <f>IF(AND(D206="",E206=""),"Yes",IF(AND(ISNUMBER(D206),ISNUMBER(E206)),IF(ABS(E206-D206)&lt;=1E-6*MAX(1,ABS(D206)),"Yes","No"),IF(D206=E206,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>sceptical Test first, then follow the rule</t>
+        </is>
+      </c>
+      <c r="D207" s="52" t="n">
+        <v>573025.7784560476</v>
+      </c>
+      <c r="E207" s="53">
+        <f>'Value of test'!B18</f>
+        <v/>
+      </c>
+      <c r="F207" s="54">
+        <f>IF(AND(ISNUMBER(D207),ISNUMBER(E207)),E207-D207,"")</f>
+        <v/>
+      </c>
+      <c r="G207" s="5">
+        <f>IF(AND(D207="",E207=""),"Yes",IF(AND(ISNUMBER(D207),ISNUMBER(E207)),IF(ABS(E207-D207)&lt;=1E-6*MAX(1,ABS(D207)),"Yes","No"),IF(D207=E207,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>optimistic Test first, then follow the rule</t>
+        </is>
+      </c>
+      <c r="D208" s="52" t="n">
+        <v>1609448.328269738</v>
+      </c>
+      <c r="E208" s="53">
+        <f>'Value of test'!C18</f>
+        <v/>
+      </c>
+      <c r="F208" s="54">
+        <f>IF(AND(ISNUMBER(D208),ISNUMBER(E208)),E208-D208,"")</f>
+        <v/>
+      </c>
+      <c r="G208" s="5">
+        <f>IF(AND(D208="",E208=""),"Yes",IF(AND(ISNUMBER(D208),ISNUMBER(E208)),IF(ABS(E208-D208)&lt;=1E-6*MAX(1,ABS(D208)),"Yes","No"),IF(D208=E208,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>sceptical Value of perfect information</t>
+        </is>
+      </c>
+      <c r="D209" s="52" t="n">
+        <v>1320278.508040935</v>
+      </c>
+      <c r="E209" s="53">
+        <f>'Value of test'!B19</f>
+        <v/>
+      </c>
+      <c r="F209" s="54">
+        <f>IF(AND(ISNUMBER(D209),ISNUMBER(E209)),E209-D209,"")</f>
+        <v/>
+      </c>
+      <c r="G209" s="5">
+        <f>IF(AND(D209="",E209=""),"Yes",IF(AND(ISNUMBER(D209),ISNUMBER(E209)),IF(ABS(E209-D209)&lt;=1E-6*MAX(1,ABS(D209)),"Yes","No"),IF(D209=E209,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>optimistic Value of perfect information</t>
+        </is>
+      </c>
+      <c r="D210" s="52" t="n">
+        <v>668736.6975816977</v>
+      </c>
+      <c r="E210" s="53">
+        <f>'Value of test'!C19</f>
+        <v/>
+      </c>
+      <c r="F210" s="54">
+        <f>IF(AND(ISNUMBER(D210),ISNUMBER(E210)),E210-D210,"")</f>
+        <v/>
+      </c>
+      <c r="G210" s="5">
+        <f>IF(AND(D210="",E210=""),"Yes",IF(AND(ISNUMBER(D210),ISNUMBER(E210)),IF(ABS(E210-D210)&lt;=1E-6*MAX(1,ABS(D210)),"Yes","No"),IF(D210=E210,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>sceptical value of running the test</t>
+        </is>
+      </c>
+      <c r="D211" s="52" t="n">
+        <v>573025.7784560476</v>
+      </c>
+      <c r="E211" s="53">
+        <f>'Value of test'!B20</f>
+        <v/>
+      </c>
+      <c r="F211" s="54">
+        <f>IF(AND(ISNUMBER(D211),ISNUMBER(E211)),E211-D211,"")</f>
+        <v/>
+      </c>
+      <c r="G211" s="5">
+        <f>IF(AND(D211="",E211=""),"Yes",IF(AND(ISNUMBER(D211),ISNUMBER(E211)),IF(ABS(E211-D211)&lt;=1E-6*MAX(1,ABS(D211)),"Yes","No"),IF(D211=E211,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>sceptical best option</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>Test first</t>
+        </is>
+      </c>
+      <c r="E212" s="6">
+        <f>'Value of test'!B21</f>
+        <v/>
+      </c>
+      <c r="F212" s="54">
+        <f>IF(AND(ISNUMBER(D212),ISNUMBER(E212)),E212-D212,"")</f>
+        <v/>
+      </c>
+      <c r="G212" s="5">
+        <f>IF(AND(D212="",E212=""),"Yes",IF(AND(ISNUMBER(D212),ISNUMBER(E212)),IF(ABS(E212-D212)&lt;=1E-6*MAX(1,ABS(D212)),"Yes","No"),IF(D212=E212,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>optimistic value of running the test</t>
+        </is>
+      </c>
+      <c r="D213" s="52" t="n">
+        <v>-115642.318470435</v>
+      </c>
+      <c r="E213" s="53">
+        <f>'Value of test'!C20</f>
+        <v/>
+      </c>
+      <c r="F213" s="54">
+        <f>IF(AND(ISNUMBER(D213),ISNUMBER(E213)),E213-D213,"")</f>
+        <v/>
+      </c>
+      <c r="G213" s="5">
+        <f>IF(AND(D213="",E213=""),"Yes",IF(AND(ISNUMBER(D213),ISNUMBER(E213)),IF(ABS(E213-D213)&lt;=1E-6*MAX(1,ABS(D213)),"Yes","No"),IF(D213=E213,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Value of test</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>optimistic best option</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>Launch now</t>
+        </is>
+      </c>
+      <c r="E214" s="6">
+        <f>'Value of test'!C21</f>
+        <v/>
+      </c>
+      <c r="F214" s="54">
+        <f>IF(AND(ISNUMBER(D214),ISNUMBER(E214)),E214-D214,"")</f>
+        <v/>
+      </c>
+      <c r="G214" s="5">
+        <f>IF(AND(D214="",E214=""),"Yes",IF(AND(ISNUMBER(D214),ISNUMBER(E214)),IF(ABS(E214-D214)&lt;=1E-6*MAX(1,ABS(D214)),"Yes","No"),IF(D214=E214,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>Smallest feasible test</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>180 days, one-sided</t>
+        </is>
+      </c>
+      <c r="E215" s="6">
+        <f>Summary!B10</f>
+        <v/>
+      </c>
+      <c r="F215" s="54">
+        <f>IF(AND(ISNUMBER(D215),ISNUMBER(E215)),E215-D215,"")</f>
+        <v/>
+      </c>
+      <c r="G215" s="5">
+        <f>IF(AND(D215="",E215=""),"Yes",IF(AND(ISNUMBER(D215),ISNUMBER(E215)),IF(ABS(E215-D215)&lt;=1E-6*MAX(1,ABS(D215)),"Yes","No"),IF(D215=E215,"Yes","No")))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G7:G192">
+  <conditionalFormatting sqref="G7:G215">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"Yes"</formula>
     </cfRule>
@@ -8744,6 +10002,384 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Is the test worth running?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Each option's expected value under a prior belief about the real uplift. NPV is linear in the uplift, so it comes straight from the business case; the chance that the test says 'Scale' comes from simulated tests (blue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Test window, days</t>
+        </is>
+      </c>
+      <c r="B4" s="6">
+        <f>INDEX('Test design'!B5:B8,MATCH("Yes",'Test design'!L5:L8,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cost of the test (build, outreach to the treated half, one account executive)</t>
+        </is>
+      </c>
+      <c r="B5" s="24">
+        <f>'Business case'!$B$10/2*Inputs!$C$13*B4/365+1*Inputs!$C$10*B4/365+Inputs!$C$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Delay factor for value after the test</t>
+        </is>
+      </c>
+      <c r="B6" s="25">
+        <f>1/(1+Inputs!$C$16)^(B4/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>True uplift</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Prior: sceptical</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Prior: optimistic</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>NPV if launched now</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Chance the test says Scale</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Value if scaled after the test</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Test-first value</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>NPV, if positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" s="38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="24">
+        <f>'Business case'!$B$35*A9-'Business case'!$B$36</f>
+        <v/>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24">
+        <f>(D9+Inputs!$C$15/(1+Inputs!$C$16))*$B$6</f>
+        <v/>
+      </c>
+      <c r="G9" s="24">
+        <f>E9*F9-$B$5</f>
+        <v/>
+      </c>
+      <c r="H9" s="24">
+        <f>MAX(0,D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="B10" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="24">
+        <f>'Business case'!$B$35*A10-'Business case'!$B$36</f>
+        <v/>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>0.1366666666666667</v>
+      </c>
+      <c r="F10" s="24">
+        <f>(D10+Inputs!$C$15/(1+Inputs!$C$16))*$B$6</f>
+        <v/>
+      </c>
+      <c r="G10" s="24">
+        <f>E10*F10-$B$5</f>
+        <v/>
+      </c>
+      <c r="H10" s="24">
+        <f>MAX(0,D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="B11" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="24">
+        <f>'Business case'!$B$35*A11-'Business case'!$B$36</f>
+        <v/>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>0.5566666666666666</v>
+      </c>
+      <c r="F11" s="24">
+        <f>(D11+Inputs!$C$15/(1+Inputs!$C$16))*$B$6</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>E11*F11-$B$5</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>MAX(0,D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B12" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="24">
+        <f>'Business case'!$B$35*A12-'Business case'!$B$36</f>
+        <v/>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>0.8233333333333334</v>
+      </c>
+      <c r="F12" s="24">
+        <f>(D12+Inputs!$C$15/(1+Inputs!$C$16))*$B$6</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>E12*F12-$B$5</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>MAX(0,D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="B13" s="38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="24">
+        <f>'Business case'!$B$35*A13-'Business case'!$B$36</f>
+        <v/>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F13" s="24">
+        <f>(D13+Inputs!$C$15/(1+Inputs!$C$16))*$B$6</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>E13*F13-$B$5</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>MAX(0,D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Under the prior</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>sceptical</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Launch now</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>SUMPRODUCT(B9:B13,D9:D13)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUMPRODUCT(C9:C13,D9:D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Do nothing</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C17" s="24">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Test first, then follow the rule</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>SUMPRODUCT(B9:B13,G9:G13)</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>SUMPRODUCT(C9:C13,G9:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Value of perfect information</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>SUMPRODUCT(B9:B13,H9:H13)-MAX(0,SUMPRODUCT(B9:B13,D9:D13))</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>SUMPRODUCT(C9:C13,H9:H13)-MAX(0,SUMPRODUCT(C9:C13,D9:D13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Value of running the test</t>
+        </is>
+      </c>
+      <c r="B20" s="40">
+        <f>B18-MAX(0,B16)</f>
+        <v/>
+      </c>
+      <c r="C20" s="40">
+        <f>C18-MAX(0,C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Best option</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>IF(AND(B18&gt;=B16,B18&gt;=0),"Test first",IF(B16&gt;=0,"Launch now","Do nothing"))</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>IF(AND(C18&gt;=C16,C18&gt;=0),"Test first",IF(C16&gt;=0,"Launch now","Do nothing"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>The test's own upgrades are not counted, which understates its value slightly. The chance of 'Scale' at an uplift below break-even is the rule's cost: it can scale a bet that loses.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8835,11 +10471,11 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2021|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -8855,7 +10491,7 @@
         <f>E5-D5-F5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="42">
         <f>E5-D5</f>
         <v/>
       </c>
@@ -8876,11 +10512,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2021|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -8896,7 +10532,7 @@
         <f>E6-D6-F6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="42">
         <f>E6-D6</f>
         <v/>
       </c>
@@ -8917,11 +10553,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2021|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -8937,7 +10573,7 @@
         <f>E7-D7-F7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="42">
         <f>E7-D7</f>
         <v/>
       </c>
@@ -8958,11 +10594,11 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -8978,7 +10614,7 @@
         <f>E8-D8-F8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="42">
         <f>E8-D8</f>
         <v/>
       </c>
@@ -8999,11 +10635,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9019,7 +10655,7 @@
         <f>E9-D9-F9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="42">
         <f>E9-D9</f>
         <v/>
       </c>
@@ -9040,11 +10676,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2022|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9060,7 +10696,7 @@
         <f>E10-D10-F10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="42">
         <f>E10-D10</f>
         <v/>
       </c>
@@ -9081,11 +10717,11 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2024|Self-Serve &amp; Add-Ons",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9101,7 +10737,7 @@
         <f>E11-D11-F11-G11</f>
         <v/>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="42">
         <f>E11-D11</f>
         <v/>
       </c>
@@ -9122,11 +10758,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2024|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9142,7 +10778,7 @@
         <f>E12-D12-F12-G12</f>
         <v/>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="42">
         <f>E12-D12</f>
         <v/>
       </c>
@@ -9163,11 +10799,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2023|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2022|2024|Other",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9183,7 +10819,7 @@
         <f>E13-D13-F13-G13</f>
         <v/>
       </c>
-      <c r="I13" s="38">
+      <c r="I13" s="42">
         <f>E13-D13</f>
         <v/>
       </c>
@@ -9204,11 +10840,11 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q1|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q1|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9224,7 +10860,7 @@
         <f>E14-D14-F14-G14</f>
         <v/>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="42">
         <f>E14-D14</f>
         <v/>
       </c>
@@ -9245,11 +10881,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q1|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q1|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9265,7 +10901,7 @@
         <f>E15-D15-F15-G15</f>
         <v/>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="42">
         <f>E15-D15</f>
         <v/>
       </c>
@@ -9286,11 +10922,11 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q1|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q1|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9306,7 +10942,7 @@
         <f>E16-D16-F16-G16</f>
         <v/>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="42">
         <f>E16-D16</f>
         <v/>
       </c>
@@ -9327,11 +10963,11 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q2|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q2|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9347,7 +10983,7 @@
         <f>E17-D17-F17-G17</f>
         <v/>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="42">
         <f>E17-D17</f>
         <v/>
       </c>
@@ -9368,11 +11004,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q2|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q2|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9388,7 +11024,7 @@
         <f>E18-D18-F18-G18</f>
         <v/>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="42">
         <f>E18-D18</f>
         <v/>
       </c>
@@ -9409,11 +11045,11 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q2|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q2|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9429,7 +11065,7 @@
         <f>E19-D19-F19-G19</f>
         <v/>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="42">
         <f>E19-D19</f>
         <v/>
       </c>
@@ -9450,11 +11086,11 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q3|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q3|Self-Serve",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9470,7 +11106,7 @@
         <f>E20-D20-F20-G20</f>
         <v/>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="42">
         <f>E20-D20</f>
         <v/>
       </c>
@@ -9491,11 +11127,11 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q3|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q3|Vimeo Enterprise",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9511,7 +11147,7 @@
         <f>E21-D21-F21-G21</f>
         <v/>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="42">
         <f>E21-D21</f>
         <v/>
       </c>
@@ -9532,11 +11168,11 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2024Q3|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="41">
         <f>INDEX(Segments!$I$5:$I$46,MATCH("2025|2025Q3|OTT",Segments!$A$5:$A$46,0))/1000</f>
         <v/>
       </c>
@@ -9552,7 +11188,7 @@
         <f>E22-D22-F22-G22</f>
         <v/>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="42">
         <f>E22-D22</f>
         <v/>
       </c>
@@ -9563,7 +11199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9676,10 +11312,10 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="43" t="n">
         <v>1554.7</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="43" t="n">
         <v>1443.6</v>
       </c>
       <c r="G5" s="33" t="n">
@@ -9720,10 +11356,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="43" t="n">
         <v>1.6</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="43" t="n">
         <v>1.2</v>
       </c>
       <c r="G6" s="33" t="n">
@@ -9764,10 +11400,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="43" t="n">
         <v>138.7</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="43" t="n">
         <v>168</v>
       </c>
       <c r="G7" s="33" t="n">
@@ -9808,10 +11444,10 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="43" t="n">
         <v>1505</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="43" t="n">
         <v>1529.9</v>
       </c>
       <c r="G8" s="33" t="n">
@@ -9852,10 +11488,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="43" t="n">
         <v>2.2</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="43" t="n">
         <v>1.9</v>
       </c>
       <c r="G9" s="33" t="n">
@@ -9896,10 +11532,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="43" t="n">
         <v>93.3</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="43" t="n">
         <v>116</v>
       </c>
       <c r="G10" s="33" t="n">
@@ -9940,10 +11576,10 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="43" t="n">
         <v>1379.7</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="43" t="n">
         <v>1442.4</v>
       </c>
       <c r="G11" s="33" t="n">
@@ -9984,10 +11620,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="43" t="n">
         <v>3.3</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="43" t="n">
         <v>2.8</v>
       </c>
       <c r="G12" s="33" t="n">
@@ -10028,10 +11664,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="43" t="n">
         <v>67</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="43" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="G13" s="33" t="n">
@@ -10072,10 +11708,10 @@
           <t>Self-Serve &amp; Add-Ons</t>
         </is>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="43" t="n">
         <v>1227.7</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="43" t="n">
         <v>1303.7</v>
       </c>
       <c r="G14" s="33" t="n">
@@ -10116,10 +11752,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="43" t="n">
         <v>3.7</v>
       </c>
       <c r="G15" s="33" t="n">
@@ -10160,10 +11796,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="43" t="n">
         <v>58.5</v>
       </c>
       <c r="G16" s="33" t="n">
@@ -10204,10 +11840,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="43" t="n">
         <v>1341.6</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="43" t="n">
         <v>1357.1</v>
       </c>
       <c r="G17" s="33" t="n">
@@ -10248,10 +11884,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="43" t="n">
         <v>3.7</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="43" t="n">
         <v>3.5</v>
       </c>
       <c r="G18" s="33" t="n">
@@ -10292,10 +11928,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="33" t="n">
@@ -10384,10 +12020,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="43" t="n">
         <v>1298.1</v>
       </c>
-      <c r="F22" s="39" t="n">
+      <c r="F22" s="43" t="n">
         <v>1319.8</v>
       </c>
       <c r="G22" s="33" t="n">
@@ -10428,10 +12064,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E23" s="39" t="n">
+      <c r="E23" s="43" t="n">
         <v>3.7</v>
       </c>
-      <c r="F23" s="39" t="n">
+      <c r="F23" s="43" t="n">
         <v>3.7</v>
       </c>
       <c r="G23" s="33" t="n">
@@ -10472,10 +12108,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E24" s="43" t="n">
         <v>2.9</v>
       </c>
-      <c r="F24" s="39" t="n">
+      <c r="F24" s="43" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="33" t="n">
@@ -10564,10 +12200,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E27" s="39" t="n">
+      <c r="E27" s="43" t="n">
         <v>1269.1</v>
       </c>
-      <c r="F27" s="39" t="n">
+      <c r="F27" s="43" t="n">
         <v>1283.6</v>
       </c>
       <c r="G27" s="33" t="n">
@@ -10608,10 +12244,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E28" s="39" t="n">
+      <c r="E28" s="43" t="n">
         <v>3.8</v>
       </c>
-      <c r="F28" s="39" t="n">
+      <c r="F28" s="43" t="n">
         <v>3.7</v>
       </c>
       <c r="G28" s="33" t="n">
@@ -10652,10 +12288,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E29" s="39" t="n">
+      <c r="E29" s="43" t="n">
         <v>3.1</v>
       </c>
-      <c r="F29" s="39" t="n">
+      <c r="F29" s="43" t="n">
         <v>3</v>
       </c>
       <c r="G29" s="33" t="n">
@@ -10744,10 +12380,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E32" s="39" t="n">
+      <c r="E32" s="43" t="n">
         <v>1189.3</v>
       </c>
-      <c r="F32" s="39" t="n">
+      <c r="F32" s="43" t="n">
         <v>1205.4</v>
       </c>
       <c r="G32" s="33" t="n">
@@ -10788,10 +12424,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E33" s="39" t="n">
+      <c r="E33" s="43" t="n">
         <v>4.1</v>
       </c>
-      <c r="F33" s="39" t="n">
+      <c r="F33" s="43" t="n">
         <v>4</v>
       </c>
       <c r="G33" s="33" t="n">
@@ -10832,10 +12468,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E34" s="39" t="n">
+      <c r="E34" s="43" t="n">
         <v>3.2</v>
       </c>
-      <c r="F34" s="39" t="n">
+      <c r="F34" s="43" t="n">
         <v>3.2</v>
       </c>
       <c r="G34" s="33" t="n">
@@ -10924,10 +12560,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E37" s="39" t="n">
+      <c r="E37" s="43" t="n">
         <v>1156.5</v>
       </c>
-      <c r="F37" s="39" t="n">
+      <c r="F37" s="43" t="n">
         <v>1172.9</v>
       </c>
       <c r="G37" s="33" t="n">
@@ -10968,10 +12604,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E38" s="39" t="n">
+      <c r="E38" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="39" t="n">
+      <c r="F38" s="43" t="n">
         <v>4.1</v>
       </c>
       <c r="G38" s="33" t="n">
@@ -11012,10 +12648,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E39" s="39" t="n">
+      <c r="E39" s="43" t="n">
         <v>3.1</v>
       </c>
-      <c r="F39" s="39" t="n">
+      <c r="F39" s="43" t="n">
         <v>3.1</v>
       </c>
       <c r="G39" s="33" t="n">
@@ -11104,10 +12740,10 @@
           <t>Self-Serve</t>
         </is>
       </c>
-      <c r="E42" s="39" t="n">
+      <c r="E42" s="43" t="n">
         <v>1127.9</v>
       </c>
-      <c r="F42" s="39" t="n">
+      <c r="F42" s="43" t="n">
         <v>1142.2</v>
       </c>
       <c r="G42" s="33" t="n">
@@ -11148,10 +12784,10 @@
           <t>Vimeo Enterprise</t>
         </is>
       </c>
-      <c r="E43" s="39" t="n">
+      <c r="E43" s="43" t="n">
         <v>4.2</v>
       </c>
-      <c r="F43" s="39" t="n">
+      <c r="F43" s="43" t="n">
         <v>4.1</v>
       </c>
       <c r="G43" s="33" t="n">
@@ -11192,10 +12828,10 @@
           <t>OTT</t>
         </is>
       </c>
-      <c r="E44" s="39" t="n">
+      <c r="E44" s="43" t="n">
         <v>3.1</v>
       </c>
-      <c r="F44" s="39" t="n">
+      <c r="F44" s="43" t="n">
         <v>3.1</v>
       </c>
       <c r="G44" s="33" t="n">
@@ -11270,626 +12906,8 @@
           <t>Largest gap</t>
         </is>
       </c>
-      <c r="K48" s="40">
+      <c r="K48" s="44">
         <f>MAX(MAX(K5:K46),-MIN(K5:K46))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>P&amp;L from XBRL facts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>US$ millions. Blue figures from data/sec_financials.csv; ratios are formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="22" t="inlineStr"/>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>2024Q1</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>2024Q2</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>2024Q3</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>2025Q1</t>
-        </is>
-      </c>
-      <c r="J4" s="22" t="inlineStr">
-        <is>
-          <t>2025Q2</t>
-        </is>
-      </c>
-      <c r="K4" s="22" t="inlineStr">
-        <is>
-          <t>2025Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="n">
-        <v>391.678</v>
-      </c>
-      <c r="C5" s="39" t="n">
-        <v>433.028</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>417.214</v>
-      </c>
-      <c r="E5" s="39" t="n">
-        <v>417.006</v>
-      </c>
-      <c r="F5" s="39" t="n">
-        <v>104.91</v>
-      </c>
-      <c r="G5" s="39" t="n">
-        <v>104.376</v>
-      </c>
-      <c r="H5" s="39" t="n">
-        <v>104.564</v>
-      </c>
-      <c r="I5" s="39" t="n">
-        <v>103.034</v>
-      </c>
-      <c r="J5" s="39" t="n">
-        <v>104.65</v>
-      </c>
-      <c r="K5" s="39" t="n">
-        <v>105.756</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Cost of revenue</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="n">
-        <v>102.537</v>
-      </c>
-      <c r="C6" s="39" t="n">
-        <v>103.595</v>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>91.57599999999999</v>
-      </c>
-      <c r="E6" s="39" t="n">
-        <v>90.73099999999999</v>
-      </c>
-      <c r="F6" s="39" t="n">
-        <v>23.443</v>
-      </c>
-      <c r="G6" s="39" t="n">
-        <v>22.678</v>
-      </c>
-      <c r="H6" s="39" t="n">
-        <v>21.708</v>
-      </c>
-      <c r="I6" s="39" t="n">
-        <v>24.054</v>
-      </c>
-      <c r="J6" s="39" t="n">
-        <v>23.147</v>
-      </c>
-      <c r="K6" s="39" t="n">
-        <v>23.414</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Sales and marketing</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="n">
-        <v>152.691</v>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>170.401</v>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>151.487</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>119.869</v>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>32.305</v>
-      </c>
-      <c r="G7" s="39" t="n">
-        <v>27.676</v>
-      </c>
-      <c r="H7" s="39" t="n">
-        <v>28.799</v>
-      </c>
-      <c r="I7" s="39" t="n">
-        <v>33.358</v>
-      </c>
-      <c r="J7" s="39" t="n">
-        <v>30.26</v>
-      </c>
-      <c r="K7" s="39" t="n">
-        <v>30.44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="n">
-        <v>105.586</v>
-      </c>
-      <c r="C8" s="39" t="n">
-        <v>127.661</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>107.074</v>
-      </c>
-      <c r="E8" s="39" t="n">
-        <v>109.373</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>28.135</v>
-      </c>
-      <c r="G8" s="39" t="n">
-        <v>26.972</v>
-      </c>
-      <c r="H8" s="39" t="n">
-        <v>26.588</v>
-      </c>
-      <c r="I8" s="39" t="n">
-        <v>31.186</v>
-      </c>
-      <c r="J8" s="39" t="n">
-        <v>29.789</v>
-      </c>
-      <c r="K8" s="39" t="n">
-        <v>31.208</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="n">
-        <v>85.111</v>
-      </c>
-      <c r="C9" s="39" t="n">
-        <v>107.011</v>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>49.194</v>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>76.604</v>
-      </c>
-      <c r="F9" s="39" t="n">
-        <v>18.034</v>
-      </c>
-      <c r="G9" s="39" t="n">
-        <v>19.087</v>
-      </c>
-      <c r="H9" s="39" t="n">
-        <v>19.655</v>
-      </c>
-      <c r="I9" s="39" t="n">
-        <v>20.137</v>
-      </c>
-      <c r="J9" s="39" t="n">
-        <v>17.194</v>
-      </c>
-      <c r="K9" s="39" t="n">
-        <v>24.832</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="n">
-        <v>-61.016</v>
-      </c>
-      <c r="C10" s="39" t="n">
-        <v>-82.938</v>
-      </c>
-      <c r="D10" s="39" t="n">
-        <v>13.047</v>
-      </c>
-      <c r="E10" s="39" t="n">
-        <v>18.683</v>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>2.589</v>
-      </c>
-      <c r="G10" s="39" t="n">
-        <v>7.461</v>
-      </c>
-      <c r="H10" s="39" t="n">
-        <v>7.365</v>
-      </c>
-      <c r="I10" s="39" t="n">
-        <v>-6.092</v>
-      </c>
-      <c r="J10" s="39" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="K10" s="39" t="n">
-        <v>-4.591</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Advertising</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="C11" s="39" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="D11" s="39" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="E11" s="39" t="n">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B13" s="41">
-        <f>1-B6/B5</f>
-        <v/>
-      </c>
-      <c r="C13" s="41">
-        <f>1-C6/C5</f>
-        <v/>
-      </c>
-      <c r="D13" s="41">
-        <f>1-D6/D5</f>
-        <v/>
-      </c>
-      <c r="E13" s="41">
-        <f>1-E6/E5</f>
-        <v/>
-      </c>
-      <c r="F13" s="41">
-        <f>1-F6/F5</f>
-        <v/>
-      </c>
-      <c r="G13" s="41">
-        <f>1-G6/G5</f>
-        <v/>
-      </c>
-      <c r="H13" s="41">
-        <f>1-H6/H5</f>
-        <v/>
-      </c>
-      <c r="I13" s="41">
-        <f>1-I6/I5</f>
-        <v/>
-      </c>
-      <c r="J13" s="41">
-        <f>1-J6/J5</f>
-        <v/>
-      </c>
-      <c r="K13" s="41">
-        <f>1-K6/K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Sales and marketing, % revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="41">
-        <f>B7/B5</f>
-        <v/>
-      </c>
-      <c r="C14" s="41">
-        <f>C7/C5</f>
-        <v/>
-      </c>
-      <c r="D14" s="41">
-        <f>D7/D5</f>
-        <v/>
-      </c>
-      <c r="E14" s="41">
-        <f>E7/E5</f>
-        <v/>
-      </c>
-      <c r="F14" s="41">
-        <f>F7/F5</f>
-        <v/>
-      </c>
-      <c r="G14" s="41">
-        <f>G7/G5</f>
-        <v/>
-      </c>
-      <c r="H14" s="41">
-        <f>H7/H5</f>
-        <v/>
-      </c>
-      <c r="I14" s="41">
-        <f>I7/I5</f>
-        <v/>
-      </c>
-      <c r="J14" s="41">
-        <f>J7/J5</f>
-        <v/>
-      </c>
-      <c r="K14" s="41">
-        <f>K7/K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Research and development, % revenue</t>
-        </is>
-      </c>
-      <c r="B15" s="41">
-        <f>B8/B5</f>
-        <v/>
-      </c>
-      <c r="C15" s="41">
-        <f>C8/C5</f>
-        <v/>
-      </c>
-      <c r="D15" s="41">
-        <f>D8/D5</f>
-        <v/>
-      </c>
-      <c r="E15" s="41">
-        <f>E8/E5</f>
-        <v/>
-      </c>
-      <c r="F15" s="41">
-        <f>F8/F5</f>
-        <v/>
-      </c>
-      <c r="G15" s="41">
-        <f>G8/G5</f>
-        <v/>
-      </c>
-      <c r="H15" s="41">
-        <f>H8/H5</f>
-        <v/>
-      </c>
-      <c r="I15" s="41">
-        <f>I8/I5</f>
-        <v/>
-      </c>
-      <c r="J15" s="41">
-        <f>J8/J5</f>
-        <v/>
-      </c>
-      <c r="K15" s="41">
-        <f>K8/K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>General and administrative, % revenue</t>
-        </is>
-      </c>
-      <c r="B16" s="41">
-        <f>B9/B5</f>
-        <v/>
-      </c>
-      <c r="C16" s="41">
-        <f>C9/C5</f>
-        <v/>
-      </c>
-      <c r="D16" s="41">
-        <f>D9/D5</f>
-        <v/>
-      </c>
-      <c r="E16" s="41">
-        <f>E9/E5</f>
-        <v/>
-      </c>
-      <c r="F16" s="41">
-        <f>F9/F5</f>
-        <v/>
-      </c>
-      <c r="G16" s="41">
-        <f>G9/G5</f>
-        <v/>
-      </c>
-      <c r="H16" s="41">
-        <f>H9/H5</f>
-        <v/>
-      </c>
-      <c r="I16" s="41">
-        <f>I9/I5</f>
-        <v/>
-      </c>
-      <c r="J16" s="41">
-        <f>J9/J5</f>
-        <v/>
-      </c>
-      <c r="K16" s="41">
-        <f>K9/K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Operating margin</t>
-        </is>
-      </c>
-      <c r="B17" s="41">
-        <f>B10/B5</f>
-        <v/>
-      </c>
-      <c r="C17" s="41">
-        <f>C10/C5</f>
-        <v/>
-      </c>
-      <c r="D17" s="41">
-        <f>D10/D5</f>
-        <v/>
-      </c>
-      <c r="E17" s="41">
-        <f>E10/E5</f>
-        <v/>
-      </c>
-      <c r="F17" s="41">
-        <f>F10/F5</f>
-        <v/>
-      </c>
-      <c r="G17" s="41">
-        <f>G10/G5</f>
-        <v/>
-      </c>
-      <c r="H17" s="41">
-        <f>H10/H5</f>
-        <v/>
-      </c>
-      <c r="I17" s="41">
-        <f>I10/I5</f>
-        <v/>
-      </c>
-      <c r="J17" s="41">
-        <f>J10/J5</f>
-        <v/>
-      </c>
-      <c r="K17" s="41">
-        <f>K10/K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Advertising, % revenue</t>
-        </is>
-      </c>
-      <c r="B18" s="41">
-        <f>IF(B11="","",B11/B5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="41">
-        <f>IF(C11="","",C11/C5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="41">
-        <f>IF(D11="","",D11/D5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="41">
-        <f>IF(E11="","",E11/E5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="41">
-        <f>IF(F11="","",F11/F5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="41">
-        <f>IF(G11="","",G11/G5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="41">
-        <f>IF(H11="","",H11/H5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="41">
-        <f>IF(I11="","",I11/I5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="41">
-        <f>IF(J11="","",J11/J5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="41">
-        <f>IF(K11="","",K11/K5)</f>
         <v/>
       </c>
     </row>
